--- a/shabbatot/2026-10-16.xlsx
+++ b/shabbatot/2026-10-16.xlsx
@@ -2322,7 +2322,7 @@
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק, אוריה תעשה, רועי צבי סרי, איתי בן מנחם, טליה קור</t>
+          <t>משה אוברשטיין, עופר בביוף, ירדן בן שחר, איתן כהן, כליל בלאוקופף</t>
         </is>
       </c>
       <c r="H11" s="48" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, איתמר אסנהיים, חיים שמאי</t>
+          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
         </is>
       </c>
       <c r="H14" s="48" t="n"/>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין, רוני פרנקל, איתמר אסנהיים, חיים שמאי</t>
+          <t>של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
         </is>
       </c>
       <c r="H16" s="48" t="n"/>
@@ -2566,7 +2566,7 @@
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף, הילי אלפסי, נגה שוהם, נדב טוקר, איתן וינסטון, שי- לי וולגמוט, הילה עזרא</t>
+          <t>נגה שוהם, נדב טוקר, איתמר אסנהיים, איתן וינסטון, חיים שמאי, שי- לי וולגמוט, הילה עזרא</t>
         </is>
       </c>
       <c r="H17" s="48" t="n"/>
@@ -2606,7 +2606,7 @@
       </c>
       <c r="G18" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, מעיין יוספי, ניתאי שלום</t>
+          <t>מעיין יוספי, יונתן לירז, ניתאי שלום</t>
         </is>
       </c>
       <c r="H18" s="48" t="n"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, מעיין רחל דינר, מעיין יוספי</t>
+          <t>אביה וייל, מעיין יוספי, יונתן לירז</t>
         </is>
       </c>
       <c r="H19" s="48" t="n"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, יונתן לירז, מעיין רחל דינר</t>
+          <t>ניתאי שלום, אביה וייל, מעיין יוספי</t>
         </is>
       </c>
       <c r="H20" s="48" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, ניתאי שלום, יונתן לירז, מעיין רחל דינר</t>
+          <t>יונתן לירז, ניתאי שלום, אביה וייל, מעיין יוספי</t>
         </is>
       </c>
       <c r="H21" s="48" t="n"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, ניתאי שלום, יונתן לירז</t>
+          <t>יונתן לירז, ניתאי שלום, אביה וייל</t>
         </is>
       </c>
       <c r="H22" s="48" t="n"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, ניצן גמלא, הלל פינגולד, ינון לוי, ארבל פרנקו</t>
+          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
         </is>
       </c>
       <c r="H23" s="48" t="n"/>
@@ -2846,7 +2846,7 @@
       <c r="F24" s="53" t="n"/>
       <c r="G24" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, ניצן גמלא, הלל פינגולד, ינון לוי, ארבל פרנקו</t>
+          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
         </is>
       </c>
       <c r="H24" s="48" t="n"/>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, יואב אוחנה</t>
+          <t>מאיה פקטר, עמית סיילס</t>
         </is>
       </c>
       <c r="H25" s="48" t="n"/>
@@ -2926,7 +2926,7 @@
       </c>
       <c r="G26" s="31" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="H26" s="48" t="n"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, רגב שהם, הילה לביא</t>
+          <t>אוריה תעשה, רותם דרור, מאיה פקטר</t>
         </is>
       </c>
       <c r="H27" s="48" t="n"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>יואב אוחנה, אביה וייל</t>
+          <t>עמית סיילס, נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="H28" s="48" t="n"/>
@@ -3042,7 +3042,7 @@
       <c r="F29" s="53" t="n"/>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, יואב אוחנה, אביה וייל, אלרואי גרינברג, רגב שהם</t>
+          <t>מאיה פקטר, עמית סיילס, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
         </is>
       </c>
       <c r="H29" s="48" t="n"/>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="H30" s="48" t="n"/>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="G31" s="31" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="H31" s="48" t="n"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>בניה מעוז</t>
         </is>
       </c>
       <c r="H32" s="48" t="n"/>
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="H33" s="48" t="n"/>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="G34" s="31" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="H34" s="48" t="n"/>
@@ -3282,7 +3282,7 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, עמית סיילס</t>
+          <t>הדר עמדי, רוני כהן</t>
         </is>
       </c>
       <c r="H35" s="48" t="n"/>
@@ -3322,7 +3322,7 @@
       </c>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>קובי סמייסון, עמית שי אברהם</t>
+          <t>מעיין רחל דינר, אחיה נחמני</t>
         </is>
       </c>
       <c r="H36" s="48" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G37" s="31" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, עמית סיילס</t>
+          <t>הדר עמדי, רוני כהן</t>
         </is>
       </c>
       <c r="H37" s="48" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="G38" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, שחר קרן, שירה ספונוב, אלה גוטליב, אחיה נחמני</t>
+          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
         </is>
       </c>
       <c r="H38" s="48" t="n"/>
@@ -3442,7 +3442,7 @@
       <c r="F39" s="53" t="n"/>
       <c r="G39" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, שחר קרן, שירה ספונוב, אלה גוטליב, אחיה נחמני</t>
+          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
         </is>
       </c>
       <c r="H39" s="48" t="n"/>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G40" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, שחר קרן</t>
+          <t>שירה ספונוב, קובי סמייסון</t>
         </is>
       </c>
       <c r="H40" s="48" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G41" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה, מעיין יוספי, ינון לוי, ארבל פרנקו, נגה חוה כהן, יהב לוי, תמר פרימור, ירדן בן שחר, הילי אלפסי</t>
+          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, אביה וייל, ארבל פרנקו, יואב אוחנה, ינון לוי, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
         </is>
       </c>
       <c r="H41" s="48" t="n"/>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="G42" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, נבו בלוך, שילת פילפל, אלה מאיר, תמר פרידמן, רותם דרור, עופר בביוף, נועם ישראל קומפאס, כליל בלאוקופף, איתן כהן, של״ו רובינשטיין, אנה עזריאל</t>
+          <t>רועי צבי סרי, יהב לוי, יובל יצחק, הילי אלפסי, שילת פילפל, רוני פרנקל, אנה עזריאל, טליה קור, של״ו רובינשטיין, איתי בן מנחם, אלה מאיר, שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="H42" s="48" t="n"/>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="E4" s="31" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="E10" s="31" t="inlineStr">
@@ -4907,12 +4907,12 @@
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>אוריה תעשה</t>
         </is>
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, איתמר אסנהיים, חיים שמאי</t>
+          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
         </is>
       </c>
       <c r="F11" s="50">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>איתן וינסטון</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף, הילי אלפסי, נגה שוהם, נדב טוקר, איתן וינסטון, שי- לי וולגמוט, הילה עזרא</t>
+          <t>נגה שוהם, נדב טוקר, איתמר אסנהיים, איתן וינסטון, חיים שמאי, שי- לי וולגמוט, הילה עזרא</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -4973,12 +4973,12 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, מעיין יוספי, ניתאי שלום, יונתן לירז</t>
+          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל</t>
         </is>
       </c>
       <c r="F13" s="50">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="E14" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, ניצן גמלא, הלל פינגולד, ינון לוי, ארבל פרנקו</t>
+          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5039,12 +5039,12 @@
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, יואב אוחנה, אביה וייל, אלרואי גרינברג, רגב שהם</t>
+          <t>מאיה פקטר, עמית סיילס, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="E16" s="31" t="inlineStr">
         <is>
-          <t>יובל יצחק, הדר עמדי, רוני כהן, זואי כהן, יערה ריס</t>
+          <t>ניצן גמלא, הלל פינגולד, בניה מעוז, אלרואי גרינברג, רגב שהם</t>
         </is>
       </c>
       <c r="F16" s="50">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים, עמית סיילס, קובי סמייסון, עמית שי אברהם</t>
+          <t>הדר עמדי, רוני כהן, מעיין רחל דינר, אחיה נחמני</t>
         </is>
       </c>
       <c r="F17" s="50">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, שחר קרן, שירה ספונוב, אלה גוטליב, אחיה נחמני</t>
+          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
         </is>
       </c>
       <c r="F18" s="50">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה, מעיין יוספי, ינון לוי, ארבל פרנקו, נגה חוה כהן, יהב לוי, תמר פרימור, ירדן בן שחר, הילי אלפסי</t>
+          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, אביה וייל, ארבל פרנקו, יואב אוחנה, ינון לוי, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, נבו בלוך, שילת פילפל, אלה מאיר, תמר פרידמן, רותם דרור, עופר בביוף, נועם ישראל קומפאס, כליל בלאוקופף, איתן כהן, של״ו רובינשטיין, אנה עזריאל</t>
+          <t>רועי צבי סרי, יהב לוי, יובל יצחק, הילי אלפסי, שילת פילפל, רוני פרנקל, אנה עזריאל, טליה קור, של״ו רובינשטיין, איתי בן מנחם, אלה מאיר, שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="F20" s="50">
@@ -5237,12 +5237,12 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק, אוריה תעשה, רועי צבי סרי, איתי בן מנחם, טליה קור</t>
+          <t>משה אוברשטיין, עופר בביוף, ירדן בן שחר, איתן כהן, כליל בלאוקופף</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; קידוש</t>
+          <t>ארוחת צהריים שישי; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F5" s="50">
@@ -5625,7 +5625,7 @@
         <v/>
       </c>
       <c r="G5" s="35" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" s="50">
         <f>IF(A5="","",SUMIF('היסטוריה'!$B$3:$B$3002,A5,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5656,7 +5656,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי; ניקיון בית המדרש</t>
+          <t>בית מדרש; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -5664,7 +5664,7 @@
         <v/>
       </c>
       <c r="G6" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H6" s="50">
         <f>IF(A6="","",SUMIF('היסטוריה'!$B$3:$B$3002,A6,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5695,7 +5695,7 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>סלט חצילים; ניקיון בית המדרש</t>
+          <t>סלט חצילים; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -5703,7 +5703,7 @@
         <v/>
       </c>
       <c r="G7" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H7" s="50">
         <f>IF(A7="","",SUMIF('היסטוריה'!$B$3:$B$3002,A7,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; פינוי ארוחת צהריים שבת</t>
+          <t>עוגת שוקולד; פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="F8" s="50">
@@ -5773,7 +5773,7 @@
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון בית המדרש</t>
+          <t>ארוחת צהריים שישי; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F9" s="50">
@@ -5781,7 +5781,7 @@
         <v/>
       </c>
       <c r="G9" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H9" s="50">
         <f>IF(A9="","",SUMIF('היסטוריה'!$B$3:$B$3002,A9,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; פינוי ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; הכנת ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F10" s="50">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; הכנת ארוחת צהריים שבת</t>
+          <t>עוגת שוקולד; טיש</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -5898,7 +5898,7 @@
         <v/>
       </c>
       <c r="G12" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H12" s="50">
         <f>IF(A12="","",SUMIF('היסטוריה'!$B$3:$B$3002,A12,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5997,7 +5997,7 @@
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
+          <t>בית מדרש; טיש</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -6005,7 +6005,7 @@
         <v/>
       </c>
       <c r="G15" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H15" s="50">
         <f>IF(A15="","",SUMIF('היסטוריה'!$B$3:$B$3002,A15,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; קידוש</t>
+          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -6151,7 +6151,7 @@
         <v/>
       </c>
       <c r="G19" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H19" s="50">
         <f>IF(A19="","",SUMIF('היסטוריה'!$B$3:$B$3002,A19,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F20" s="50">
@@ -6190,7 +6190,7 @@
         <v/>
       </c>
       <c r="G20" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="50">
         <f>IF(A20="","",SUMIF('היסטוריה'!$B$3:$B$3002,A20,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל</t>
+          <t>עוגיות שוקולד צ'יפס; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -6295,7 +6295,7 @@
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>חלות; פינוי ארוחת ערב</t>
+          <t>חלות; קידוש</t>
         </is>
       </c>
       <c r="F23" s="50">
@@ -6303,7 +6303,7 @@
         <v/>
       </c>
       <c r="G23" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H23" s="50">
         <f>IF(A23="","",SUMIF('היסטוריה'!$B$3:$B$3002,A23,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6330,7 +6330,7 @@
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
+          <t>בית מדרש; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F24" s="50">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F25" s="50">
@@ -6447,7 +6447,7 @@
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>חלות; טיש</t>
+          <t>חלות; קידוש</t>
         </is>
       </c>
       <c r="F27" s="50">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; פינוי ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="F28" s="50">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="F29" s="50">
@@ -6533,7 +6533,7 @@
         <v/>
       </c>
       <c r="G29" s="35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H29" s="50">
         <f>IF(A29="","",SUMIF('היסטוריה'!$B$3:$B$3002,A29,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6661,7 +6661,7 @@
       </c>
       <c r="E33" s="34" t="inlineStr">
         <is>
-          <t>חלות; פינוי ארוחת ערב</t>
+          <t>חלות; קידוש</t>
         </is>
       </c>
       <c r="F33" s="50">
@@ -6669,7 +6669,7 @@
         <v/>
       </c>
       <c r="G33" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H33" s="50">
         <f>IF(A33="","",SUMIF('היסטוריה'!$B$3:$B$3002,A33,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6700,7 +6700,7 @@
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; הכנת ארוחת ערב</t>
+          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F34" s="50">
@@ -6803,7 +6803,7 @@
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; הכנת ארוחת צהריים שבת</t>
+          <t>מטבוחה; פינוי ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F37" s="50">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; קידוש</t>
+          <t>עוגת שוקולד; פינוי ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F41" s="50">
@@ -6967,7 +6967,7 @@
         <v/>
       </c>
       <c r="G41" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H41" s="50">
         <f>IF(A41="","",SUMIF('היסטוריה'!$B$3:$B$3002,A41,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7037,7 +7037,7 @@
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי; ניקיון חדר האוכל</t>
+          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F43" s="50">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>בית מדרש; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F44" s="50">
@@ -7084,7 +7084,7 @@
         <v/>
       </c>
       <c r="G44" s="35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H44" s="50">
         <f>IF(A44="","",SUMIF('היסטוריה'!$B$3:$B$3002,A44,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; טיש</t>
+          <t>בית מדרש; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F46" s="50">
@@ -7152,7 +7152,7 @@
         <v/>
       </c>
       <c r="G46" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H46" s="50">
         <f>IF(A46="","",SUMIF('היסטוריה'!$B$3:$B$3002,A46,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; הכנת ארוחת צהריים שבת</t>
+          <t>עוגת שוקולד; פינוי ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F47" s="50">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ניקיון חדר האוכל</t>
+          <t>מטבוחה; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F49" s="50">
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="G49" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H49" s="50">
         <f>IF(A49="","",SUMIF('היסטוריה'!$B$3:$B$3002,A49,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7368,7 +7368,7 @@
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>בית מדרש; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F52" s="50">
@@ -7376,7 +7376,7 @@
         <v/>
       </c>
       <c r="G52" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="50">
         <f>IF(A52="","",SUMIF('היסטוריה'!$B$3:$B$3002,A52,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; הכנת ארוחת צהריים שבת</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F54" s="50">
@@ -7444,7 +7444,7 @@
         <v/>
       </c>
       <c r="G54" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H54" s="50">
         <f>IF(A54="","",SUMIF('היסטוריה'!$B$3:$B$3002,A54,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7553,7 +7553,7 @@
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>בית מדרש; טיש</t>
         </is>
       </c>
       <c r="F57" s="50">
@@ -7561,7 +7561,7 @@
         <v/>
       </c>
       <c r="G57" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H57" s="50">
         <f>IF(A57="","",SUMIF('היסטוריה'!$B$3:$B$3002,A57,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7592,7 +7592,7 @@
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ארוחת ערב מוצ"ש</t>
+          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F58" s="50">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>סלט חצילים; ניקיון חדר האוכל</t>
+          <t>סלט חצילים; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F59" s="50">
@@ -7670,7 +7670,7 @@
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ארוחת ערב מוצ"ש</t>
+          <t>מטבוחה; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F60" s="50">
@@ -7709,7 +7709,7 @@
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ארוחת ערב מוצ"ש</t>
+          <t>ארוחת צהריים שישי; ניקיון חדר האוכל</t>
         </is>
       </c>
       <c r="F61" s="50">
@@ -7748,7 +7748,7 @@
       </c>
       <c r="E62" s="34" t="inlineStr">
         <is>
-          <t>חלות; פינוי ארוחת ערב</t>
+          <t>חלות; קידוש</t>
         </is>
       </c>
       <c r="F62" s="50">
@@ -7756,7 +7756,7 @@
         <v/>
       </c>
       <c r="G62" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H62" s="50">
         <f>IF(A62="","",SUMIF('היסטוריה'!$B$3:$B$3002,A62,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון בית המדרש</t>
+          <t>הכנת ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F63" s="50">
@@ -7795,7 +7795,7 @@
         <v/>
       </c>
       <c r="G63" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="50">
         <f>IF(A63="","",SUMIF('היסטוריה'!$B$3:$B$3002,A63,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; קידוש</t>
+          <t>מטבוחה; פינוי ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F65" s="50">
@@ -7863,7 +7863,7 @@
         <v/>
       </c>
       <c r="G65" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H65" s="50">
         <f>IF(A65="","",SUMIF('היסטוריה'!$B$3:$B$3002,A65,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7981,7 +7981,7 @@
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; פינוי ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; טיש</t>
         </is>
       </c>
       <c r="F69" s="50">
@@ -7989,7 +7989,7 @@
         <v/>
       </c>
       <c r="G69" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H69" s="50">
         <f>IF(A69="","",SUMIF('היסטוריה'!$B$3:$B$3002,A69,'היסטוריה'!$E$3:$E$3002))</f>
@@ -8045,7 +8045,7 @@
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>חלות; טיש</t>
+          <t>חלות; קידוש</t>
         </is>
       </c>
       <c r="F71" s="50">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; קידוש</t>
+          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F72" s="50">
@@ -8092,7 +8092,7 @@
         <v/>
       </c>
       <c r="G72" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H72" s="50">
         <f>IF(A72="","",SUMIF('היסטוריה'!$B$3:$B$3002,A72,'היסטוריה'!$E$3:$E$3002))</f>
@@ -12121,7 +12121,7 @@
       </c>
       <c r="B130" s="59" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C130" s="60" t="inlineStr">
@@ -12144,7 +12144,7 @@
       </c>
       <c r="B131" s="59" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C131" s="60" t="inlineStr">
@@ -12167,7 +12167,7 @@
       </c>
       <c r="B132" s="59" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>כליל בלאוקופף</t>
         </is>
       </c>
       <c r="C132" s="60" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B133" s="59" t="inlineStr">
         <is>
-          <t>רועי צבי סרי</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C133" s="60" t="inlineStr">
@@ -12213,7 +12213,7 @@
       </c>
       <c r="B134" s="59" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק</t>
+          <t>עופר בביוף</t>
         </is>
       </c>
       <c r="C134" s="60" t="inlineStr">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="B137" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>הילה לביא</t>
         </is>
       </c>
       <c r="C137" s="60" t="inlineStr">
@@ -12305,7 +12305,7 @@
       </c>
       <c r="B138" s="59" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C138" s="60" t="inlineStr">
@@ -12328,7 +12328,7 @@
       </c>
       <c r="B139" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C139" s="60" t="inlineStr">
@@ -12351,7 +12351,7 @@
       </c>
       <c r="B140" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C140" s="60" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="B141" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C141" s="60" t="inlineStr">
@@ -12397,7 +12397,7 @@
       </c>
       <c r="B142" s="59" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>נבו בלוך</t>
         </is>
       </c>
       <c r="C142" s="60" t="inlineStr">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="B143" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="C143" s="60" t="inlineStr">
@@ -12443,7 +12443,7 @@
       </c>
       <c r="B144" s="59" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C144" s="60" t="inlineStr">
@@ -12466,7 +12466,7 @@
       </c>
       <c r="B145" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>תמר פרידמן</t>
         </is>
       </c>
       <c r="C145" s="60" t="inlineStr">
@@ -12512,7 +12512,7 @@
       </c>
       <c r="B147" s="59" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C147" s="60" t="inlineStr">
@@ -12581,7 +12581,7 @@
       </c>
       <c r="B150" s="59" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C150" s="60" t="inlineStr">
@@ -12604,7 +12604,7 @@
       </c>
       <c r="B151" s="59" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C151" s="60" t="inlineStr">
@@ -12627,7 +12627,7 @@
       </c>
       <c r="B152" s="59" t="inlineStr">
         <is>
-          <t>נבו בלוך</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="C152" s="60" t="inlineStr">
@@ -12650,7 +12650,7 @@
       </c>
       <c r="B153" s="59" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C153" s="60" t="inlineStr">
@@ -12673,7 +12673,7 @@
       </c>
       <c r="B154" s="59" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>רוני פרנקל</t>
         </is>
       </c>
       <c r="C154" s="60" t="inlineStr">
@@ -12696,7 +12696,7 @@
       </c>
       <c r="B155" s="59" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>רועי צבי סרי</t>
         </is>
       </c>
       <c r="C155" s="60" t="inlineStr">
@@ -12719,7 +12719,7 @@
       </c>
       <c r="B156" s="59" t="inlineStr">
         <is>
-          <t>שילת פילפל</t>
+          <t>שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="C156" s="60" t="inlineStr">
@@ -12742,7 +12742,7 @@
       </c>
       <c r="B157" s="59" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C157" s="60" t="inlineStr">
@@ -12765,7 +12765,7 @@
       </c>
       <c r="B158" s="59" t="inlineStr">
         <is>
-          <t>תמר פרידמן</t>
+          <t>של״ו רובינשטיין</t>
         </is>
       </c>
       <c r="C158" s="60" t="inlineStr">
@@ -12788,7 +12788,7 @@
       </c>
       <c r="B159" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C159" s="60" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B160" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C160" s="60" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="B161" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C161" s="60" t="inlineStr">
@@ -12880,7 +12880,7 @@
       </c>
       <c r="B163" s="59" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C163" s="60" t="inlineStr">
@@ -12903,7 +12903,7 @@
       </c>
       <c r="B164" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C164" s="60" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="B165" s="59" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C165" s="60" t="inlineStr">
@@ -12949,7 +12949,7 @@
       </c>
       <c r="B166" s="59" t="inlineStr">
         <is>
-          <t>קובי סמייסון</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C166" s="60" t="inlineStr">
@@ -12972,7 +12972,7 @@
       </c>
       <c r="B167" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>אוריה תעשה</t>
         </is>
       </c>
       <c r="C167" s="60" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="B168" s="59" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C168" s="60" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="B169" s="59" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C169" s="60" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="B170" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C170" s="60" t="inlineStr">
@@ -13064,7 +13064,7 @@
       </c>
       <c r="B171" s="59" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="C171" s="60" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B172" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C172" s="60" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B173" s="59" t="inlineStr">
         <is>
-          <t>בניה מעוז</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C173" s="60" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="B174" s="59" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C174" s="60" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B176" s="59" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>שחר קרן</t>
         </is>
       </c>
       <c r="C176" s="60" t="inlineStr">
@@ -13202,7 +13202,7 @@
       </c>
       <c r="B177" s="59" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C177" s="60" t="inlineStr">
@@ -13225,7 +13225,7 @@
       </c>
       <c r="B178" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="C178" s="60" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="B179" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C179" s="60" t="inlineStr">
@@ -13271,7 +13271,7 @@
       </c>
       <c r="B180" s="59" t="inlineStr">
         <is>
-          <t>שחר קרן</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="C180" s="60" t="inlineStr">
@@ -13317,7 +13317,7 @@
       </c>
       <c r="B182" s="59" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C182" s="60" t="inlineStr">
@@ -13340,7 +13340,7 @@
       </c>
       <c r="B183" s="59" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>בניה מעוז</t>
         </is>
       </c>
       <c r="C183" s="60" t="inlineStr">
@@ -13363,7 +13363,7 @@
       </c>
       <c r="B184" s="59" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C184" s="60" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="B185" s="59" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="C185" s="60" t="inlineStr">
@@ -13409,7 +13409,7 @@
       </c>
       <c r="B186" s="59" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C186" s="60" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="B188" s="59" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>אנה עזריאל</t>
         </is>
       </c>
       <c r="C188" s="60" t="inlineStr">
@@ -13478,7 +13478,7 @@
       </c>
       <c r="B189" s="59" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>הילה לביא</t>
         </is>
       </c>
       <c r="C189" s="60" t="inlineStr">
@@ -13501,7 +13501,7 @@
       </c>
       <c r="B190" s="59" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C190" s="60" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="B191" s="59" t="inlineStr">
         <is>
-          <t>חיים שמאי</t>
+          <t>כליל בלאוקופף</t>
         </is>
       </c>
       <c r="C191" s="60" t="inlineStr">
@@ -13708,7 +13708,7 @@
       </c>
       <c r="B199" s="59" t="inlineStr">
         <is>
-          <t>איתן וינסטון</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C199" s="60" t="inlineStr">
@@ -13731,7 +13731,7 @@
       </c>
       <c r="B200" s="59" t="inlineStr">
         <is>
-          <t>הילה עזרא</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C200" s="60" t="inlineStr">
@@ -13754,7 +13754,7 @@
       </c>
       <c r="B201" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>הילה עזרא</t>
         </is>
       </c>
       <c r="C201" s="60" t="inlineStr">
@@ -13777,7 +13777,7 @@
       </c>
       <c r="B202" s="59" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C202" s="60" t="inlineStr">

--- a/shabbatot/2026-10-16.xlsx
+++ b/shabbatot/2026-10-16.xlsx
@@ -2606,7 +2606,7 @@
       </c>
       <c r="G18" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, יונתן לירז, ניתאי שלום</t>
+          <t>אלה גוטליב, שחר קרן, מאיה פקטר</t>
         </is>
       </c>
       <c r="H18" s="48" t="n"/>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>אביה וייל, מעיין יוספי, יונתן לירז</t>
+          <t>עמית סיילס, אלה גוטליב, שחר קרן</t>
         </is>
       </c>
       <c r="H19" s="48" t="n"/>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, אביה וייל, מעיין יוספי</t>
+          <t>מאיה פקטר, עמית סיילס, אלה גוטליב</t>
         </is>
       </c>
       <c r="H20" s="48" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, אביה וייל, מעיין יוספי</t>
+          <t>שחר קרן, מאיה פקטר, עמית סיילס, אלה גוטליב</t>
         </is>
       </c>
       <c r="H21" s="48" t="n"/>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, אביה וייל</t>
+          <t>שחר קרן, מאיה פקטר, עמית סיילס</t>
         </is>
       </c>
       <c r="H22" s="48" t="n"/>
@@ -2810,7 +2810,7 @@
       </c>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
+          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
         </is>
       </c>
       <c r="H23" s="48" t="n"/>
@@ -2846,7 +2846,7 @@
       <c r="F24" s="53" t="n"/>
       <c r="G24" s="31" t="inlineStr">
         <is>
-          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
+          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
         </is>
       </c>
       <c r="H24" s="48" t="n"/>
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, עמית סיילס</t>
+          <t>ארבל פרנקו, ינון לוי</t>
         </is>
       </c>
       <c r="H25" s="48" t="n"/>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, רותם דרור, מאיה פקטר</t>
+          <t>אוריה תעשה, רותם דרור, ארבל פרנקו</t>
         </is>
       </c>
       <c r="H27" s="48" t="n"/>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>עמית סיילס, נועם ישראל קומפאס</t>
+          <t>ינון לוי, נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="H28" s="48" t="n"/>
@@ -3042,7 +3042,7 @@
       <c r="F29" s="53" t="n"/>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, עמית סיילס, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
+          <t>ארבל פרנקו, ינון לוי, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
         </is>
       </c>
       <c r="H29" s="48" t="n"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="G41" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, אביה וייל, ארבל פרנקו, יואב אוחנה, ינון לוי, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
+          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, ארבל פרנקו, ינון לוי, אביה וייל, יואב אוחנה, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
         </is>
       </c>
       <c r="H41" s="48" t="n"/>
@@ -4973,12 +4973,12 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל</t>
+          <t>אלה גוטליב, שחר קרן, מאיה פקטר, עמית סיילס</t>
         </is>
       </c>
       <c r="F13" s="50">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="D14" s="34" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="E14" s="31" t="inlineStr">
         <is>
-          <t>יואב אוחנה, ארבל פרנקו, ינון לוי, אלה גוטליב, שחר קרן</t>
+          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, עמית סיילס, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
+          <t>ארבל פרנקו, ינון לוי, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, אביה וייל, ארבל פרנקו, יואב אוחנה, ינון לוי, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
+          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, ארבל פרנקו, ינון לוי, אביה וייל, יואב אוחנה, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -5539,7 +5539,7 @@
       </c>
       <c r="E3" s="34" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F3" s="50">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; פינוי ארוחת ערב</t>
+          <t>עוגת שוקולד; הכנת ארוחת ערב</t>
         </is>
       </c>
       <c r="F8" s="50">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="E11" s="34" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F11" s="50">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; טיש</t>
+          <t>עוגת שוקולד; הכנת ארוחת ערב</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -5898,7 +5898,7 @@
         <v/>
       </c>
       <c r="G12" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H12" s="50">
         <f>IF(A12="","",SUMIF('היסטוריה'!$B$3:$B$3002,A12,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6036,7 +6036,7 @@
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F16" s="50">
@@ -6486,7 +6486,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; פינוי ארוחת ערב</t>
+          <t>עוגת שמרים; הכנת ארוחת ערב</t>
         </is>
       </c>
       <c r="F28" s="50">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>טיש; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F39" s="50">
@@ -6889,7 +6889,7 @@
         <v/>
       </c>
       <c r="G39" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H39" s="50">
         <f>IF(A39="","",SUMIF('היסטוריה'!$B$3:$B$3002,A39,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>טיש; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F50" s="50">
@@ -7308,7 +7308,7 @@
         <v/>
       </c>
       <c r="G50" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H50" s="50">
         <f>IF(A50="","",SUMIF('היסטוריה'!$B$3:$B$3002,A50,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7787,7 +7787,7 @@
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
         </is>
       </c>
       <c r="F63" s="50">
@@ -7981,7 +7981,7 @@
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; טיש</t>
+          <t>עוגת שמרים; הכנת ארוחת ערב</t>
         </is>
       </c>
       <c r="F69" s="50">
@@ -7989,7 +7989,7 @@
         <v/>
       </c>
       <c r="G69" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H69" s="50">
         <f>IF(A69="","",SUMIF('היסטוריה'!$B$3:$B$3002,A69,'היסטוריה'!$E$3:$E$3002))</f>
@@ -12788,7 +12788,7 @@
       </c>
       <c r="B159" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C159" s="60" t="inlineStr">
@@ -12811,7 +12811,7 @@
       </c>
       <c r="B160" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C160" s="60" t="inlineStr">
@@ -12834,7 +12834,7 @@
       </c>
       <c r="B161" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C161" s="60" t="inlineStr">
@@ -12857,7 +12857,7 @@
       </c>
       <c r="B162" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>שחר קרן</t>
         </is>
       </c>
       <c r="C162" s="60" t="inlineStr">
@@ -12995,7 +12995,7 @@
       </c>
       <c r="B168" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C168" s="60" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="B169" s="59" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C169" s="60" t="inlineStr">
@@ -13041,7 +13041,7 @@
       </c>
       <c r="B170" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C170" s="60" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B172" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C172" s="60" t="inlineStr">
@@ -13110,7 +13110,7 @@
       </c>
       <c r="B173" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C173" s="60" t="inlineStr">
@@ -13133,7 +13133,7 @@
       </c>
       <c r="B174" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C174" s="60" t="inlineStr">
@@ -13156,7 +13156,7 @@
       </c>
       <c r="B175" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C175" s="60" t="inlineStr">
@@ -13179,7 +13179,7 @@
       </c>
       <c r="B176" s="59" t="inlineStr">
         <is>
-          <t>שחר קרן</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C176" s="60" t="inlineStr">

--- a/shabbatot/2026-10-16.xlsx
+++ b/shabbatot/2026-10-16.xlsx
@@ -878,7 +878,7 @@
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>python3 tools/export_pdf.py &lt;תאריך&gt; — לו"ז צל + פלייר לכל קבוצת עבודה. ערכת בשיטס? הורד כ-xlsx והרץ שוב.</t>
+          <t>python3 tools/export_pdf.py &lt;תאריך&gt; — לו"ז שבת, מי בכל תורנות, ודף לכל תורנות. ערכת בשיטס? הורד כ-xlsx והרץ שוב.</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="E13" s="8" t="inlineStr">
         <is>
-          <t>גודל קבוצה = שיא האנשים שנדרשים בו-זמנית במשימות שלה. משימה בלי שעה = כל הקבוצה. משימה בלי קבוצה = בלו"ז הצל בלי שמות.</t>
+          <t>גודל קבוצה = שיא האנשים שנדרשים בו-זמנית במשימות שלה. משימה בלי שעה = כל הקבוצה. משימה בלי קבוצה = הודעה לכולם בלו"ז שבת, ליד האירוע שלה.</t>
         </is>
       </c>
     </row>
@@ -997,7 +997,7 @@
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>עוגן = האירוע בלו"ז שלידו המשימה מופיעה בלו"ז הצל. הרשימה הנגללת נלקחת מעמודת «אירוע» ב«לוז».</t>
+          <t>עוגן = האירוע בלו"ז שהמשימה קשורה אליו — ממנו השעה היחסית, ומשימה בלי שעה מוצגת בשעת האירוע. הרשימה הנגללת נלקחת מעמודת «אירוע» ב«לוז».</t>
         </is>
       </c>
     </row>
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C15" s="12" t="inlineStr">
         <is>
-          <t>לא יופיעו ליד אירוע בלו"ז הצל</t>
+          <t>בלי שעה ובלי עוגן — בדף התורנות כתוב «ללא שעה»</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
     <row r="38" ht="28" customHeight="1">
       <c r="A38" s="26" t="inlineStr">
         <is>
-          <t>«שעה» היא הלו"ז שנשלח בפועל — עורכים בה חופשי. «הצעה» מחושבת מכניסת/צאת השבת (הכללים ב-data/schedule_template.csv). «משימות» = כמה משימות מעוגנות לאירוע בלו"ז הצל.</t>
+          <t>«שעה» היא הלו"ז שנשלח בפועל — עורכים בה חופשי. «הצעה» מחושבת מכניסת/צאת השבת (הכללים ב-data/schedule_template.csv). «משימות» = כמה משימות מעוגנות לאירוע.</t>
         </is>
       </c>
     </row>
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="F3" s="53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד, בניה מעוז</t>
+          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד</t>
         </is>
       </c>
       <c r="H3" s="48" t="inlineStr">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C4" s="55" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D4" s="48" t="inlineStr">
         <is>
@@ -1982,13 +1982,9 @@
         </is>
       </c>
       <c r="F4" s="53" t="n">
-        <v>3</v>
-      </c>
-      <c r="G4" s="31" t="inlineStr">
-        <is>
-          <t>רוני כהן, מעיין רחל דינר, הדר עמדי</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G4" s="31" t="n"/>
       <c r="H4" s="48" t="inlineStr">
         <is>
           <t>בראוניז ללא גלוטן</t>
@@ -2031,11 +2027,11 @@
         </is>
       </c>
       <c r="F5" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
-          <t>זואי כהן, עמית סיילס, שחר קרן, עמית שי אברהם</t>
+          <t>בניה מעוז, רוני כהן</t>
         </is>
       </c>
       <c r="H5" s="48" t="inlineStr">
@@ -2080,11 +2076,11 @@
         </is>
       </c>
       <c r="F6" s="53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, אחיה נחמני, אלה גוטליב, מאיה פקטר</t>
+          <t>מעיין רחל דינר, הדר עמדי, זואי כהן</t>
         </is>
       </c>
       <c r="H6" s="48" t="inlineStr">
@@ -2133,7 +2129,7 @@
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>קובי סמייסון, יערה ריס, נבו בלוך, איתי בן מנחם</t>
+          <t>עמית סיילס, שחר קרן, עמית שי אברהם, שירה ספונוב</t>
         </is>
       </c>
       <c r="H7" s="48" t="inlineStr">
@@ -2165,7 +2161,7 @@
         </is>
       </c>
       <c r="C8" s="55" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D8" s="48" t="inlineStr">
         <is>
@@ -2178,13 +2174,9 @@
         </is>
       </c>
       <c r="F8" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G8" s="31" t="inlineStr">
-        <is>
-          <t>איתן כהן, יהב לוי</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="G8" s="31" t="n"/>
       <c r="H8" s="48" t="inlineStr">
         <is>
           <t>סלט חצילים</t>
@@ -2227,11 +2219,11 @@
         </is>
       </c>
       <c r="F9" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G9" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, תמר פרימור, רועי צבי סרי, עופר בביוף</t>
+          <t>אחיה נחמני, אלה גוטליב</t>
         </is>
       </c>
       <c r="H9" s="48" t="inlineStr">
@@ -2280,7 +2272,7 @@
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
-          <t>נגה חוה כהן, ירדן בן שחר, טליה קור, יובל יצחק</t>
+          <t>מאיה פקטר, קובי סמייסון, יערה ריס, נבו בלוך</t>
         </is>
       </c>
       <c r="H10" s="48" t="inlineStr">
@@ -2295,44 +2287,46 @@
       </c>
       <c r="J10" s="21" t="n"/>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="53" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
-        </is>
-      </c>
-      <c r="B11" s="56" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="C11" s="55" t="n"/>
+          <t>תורנות שישי</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C11" s="55" t="n">
+        <v>0.5833333333333334</v>
+      </c>
       <c r="D11" s="48" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב: פסטה ברוטב עגבניות</t>
+          <t>ניקיון חדר האוכל:
+שטיפת הרצפה
+ניקוי המטבח
+ניקוי חדר המקררים
+זריקת הפחים</t>
         </is>
       </c>
       <c r="F11" s="53" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, עופר בביוף, ירדן בן שחר, איתן כהן, כליל בלאוקופף</t>
-        </is>
-      </c>
-      <c r="H11" s="48" t="inlineStr">
-        <is>
-          <t>פסטה ברוטב עגבניות</t>
-        </is>
-      </c>
+          <t>נועם ישראל קומפאס, של״ו רובינשטיין, יהב לוי, נגה חוה כהן, ירדן בן שחר, כליל בלאוקופף, עופר בביוף</t>
+        </is>
+      </c>
+      <c r="H11" s="48" t="n"/>
       <c r="I11" s="48" t="inlineStr">
         <is>
-          <t>ניקיונות מוצ"ש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J11" s="21" t="n"/>
@@ -2340,39 +2334,41 @@
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="53" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
-        </is>
-      </c>
-      <c r="B12" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C12" s="55" t="n">
-        <v>0.5</v>
-      </c>
+          <t>תורנות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="B12" s="56" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="C12" s="55" t="n"/>
       <c r="D12" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E12" s="21" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
+          <t>הכנת ארוחת ערב: פסטה ברוטב עגבניות</t>
         </is>
       </c>
       <c r="F12" s="53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G12" s="31" t="inlineStr">
         <is>
-          <t>נגה חוה כהן, ירדן בן שחר</t>
-        </is>
-      </c>
-      <c r="H12" s="48" t="n"/>
+          <t>שירה ספונוב, ירדן בן שחר, רותם דרור, תמר פרידמן, איתן כהן</t>
+        </is>
+      </c>
+      <c r="H12" s="48" t="inlineStr">
+        <is>
+          <t>פסטה ברוטב עגבניות</t>
+        </is>
+      </c>
       <c r="I12" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>ניקיונות מוצ"ש</t>
         </is>
       </c>
       <c r="J12" s="21" t="n"/>
@@ -2389,7 +2385,7 @@
         </is>
       </c>
       <c r="C13" s="55" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D13" s="48" t="inlineStr">
         <is>
@@ -2398,7 +2394,7 @@
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>הגשת ארוחת הצהריים</t>
         </is>
       </c>
       <c r="F13" s="53" t="n">
@@ -2406,7 +2402,7 @@
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>טליה קור, יובל יצחק</t>
+          <t>מאיה פקטר, קובי סמייסון</t>
         </is>
       </c>
       <c r="H13" s="48" t="n"/>
@@ -2420,7 +2416,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="53" t="inlineStr">
         <is>
-          <t>תורנות שישי</t>
+          <t>הכנות שישי</t>
         </is>
       </c>
       <c r="B14" s="54" t="inlineStr">
@@ -2429,35 +2425,35 @@
         </is>
       </c>
       <c r="C14" s="55" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="D14" s="48" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>סידור בית המדרש: העברת השולחנות לכיתת בית המדרש (לא בגרירה), טאטוא ושטיפת רצפה, תליית מחיצה, סידור כסאות בשורות — כולל 3 שורות עזרת ישראל, הנחת סידורים על הכסאות</t>
+          <t>קיפול הארוחה, שטיפת כלים</t>
         </is>
       </c>
       <c r="F14" s="53" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
+          <t>יערה ריס, נבו בלוך</t>
         </is>
       </c>
       <c r="H14" s="48" t="n"/>
       <c r="I14" s="48" t="inlineStr">
         <is>
-          <t>תחילת עבודה</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J14" s="21" t="n"/>
     </row>
-    <row r="15" ht="30" customHeight="1">
+    <row r="15" ht="105" customHeight="1">
       <c r="A15" s="53" t="inlineStr">
         <is>
           <t>תורנות שישי</t>
@@ -2469,7 +2465,7 @@
         </is>
       </c>
       <c r="C15" s="55" t="n">
-        <v>0.3645833333333333</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="D15" s="48" t="inlineStr">
         <is>
@@ -2478,15 +2474,21 @@
       </c>
       <c r="E15" s="21" t="inlineStr">
         <is>
-          <t>עזרה בהכנת חלות</t>
+          <t>סידור בית המדרש:
+טאטוא ושטיפת הרצפה
+תליית המחיצה
+סידור השולחנות בשורות של 4 שולחנות בכל צד של המחיצה — 6 שורות של שולחנות עם כסאות
+מאחוריהם — כסאות לעזרת ישראל
+שאר השולחנות — לערום בקצה בית המדרש (מרימים, לא גוררים)
+הנחת סידורים על הכסאות</t>
         </is>
       </c>
       <c r="F15" s="53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס</t>
+          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן, אלה מאיר, אנה עזריאל, איתי בן מנחם, רוני פרנקל, תמר פרימור, יובל יצחק, איתן כהן</t>
         </is>
       </c>
       <c r="H15" s="48" t="n"/>
@@ -2518,7 +2520,7 @@
       </c>
       <c r="E16" s="21" t="inlineStr">
         <is>
-          <t>עזרה בהכנת עוגת שמרים</t>
+          <t>עזרה בהכנת חלות</t>
         </is>
       </c>
       <c r="F16" s="53" t="n">
@@ -2526,7 +2528,7 @@
       </c>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
+          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן</t>
         </is>
       </c>
       <c r="H16" s="48" t="n"/>
@@ -2549,30 +2551,30 @@
         </is>
       </c>
       <c r="C17" s="55" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D17" s="48" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>עזרה בהכנת בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="F17" s="53" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
-          <t>נגה שוהם, נדב טוקר, איתמר אסנהיים, איתן וינסטון, חיים שמאי, שי- לי וולגמוט, הילה עזרא</t>
+          <t>אלה מאיר, אנה עזריאל</t>
         </is>
       </c>
       <c r="H17" s="48" t="n"/>
       <c r="I17" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="J17" s="21" t="n"/>
@@ -2580,7 +2582,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="53" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B18" s="54" t="inlineStr">
@@ -2589,16 +2591,16 @@
         </is>
       </c>
       <c r="C18" s="55" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D18" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
+          <t>עזרה בהכנת עוגת שמרים</t>
         </is>
       </c>
       <c r="F18" s="53" t="n">
@@ -2606,13 +2608,13 @@
       </c>
       <c r="G18" s="31" t="inlineStr">
         <is>
-          <t>אלה גוטליב, שחר קרן, מאיה פקטר</t>
+          <t>איתי בן מנחם, רוני פרנקל, תמר פרימור</t>
         </is>
       </c>
       <c r="H18" s="48" t="n"/>
       <c r="I18" s="48" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="J18" s="21" t="n"/>
@@ -2620,7 +2622,7 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="53" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B19" s="54" t="inlineStr">
@@ -2629,30 +2631,30 @@
         </is>
       </c>
       <c r="C19" s="55" t="n">
-        <v>0.6944444444444444</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D19" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: כרעיים בגריל, אורז עם אטריות, אפונה וגזר, פלפל ממולא (טבעוני) · וחיבור מיחמים בפינת קפה</t>
+          <t>עזרה בהכנת סלט חצילים</t>
         </is>
       </c>
       <c r="F19" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>עמית סיילס, אלה גוטליב, שחר קרן</t>
+          <t>יובל יצחק, איתן כהן</t>
         </is>
       </c>
       <c r="H19" s="48" t="n"/>
       <c r="I19" s="48" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="J19" s="21" t="n"/>
@@ -2669,34 +2671,30 @@
         </is>
       </c>
       <c r="C20" s="55" t="n">
-        <v>0.78125</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>הכנת סלט כרוב מרענן, סלט טחינה ביתית</t>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
         </is>
       </c>
       <c r="F20" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, עמית סיילס, אלה גוטליב</t>
-        </is>
-      </c>
-      <c r="H20" s="48" t="inlineStr">
-        <is>
-          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
-        </is>
-      </c>
+          <t>שילת פילפל, הילי אלפסי</t>
+        </is>
+      </c>
+      <c r="H20" s="48" t="n"/>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="J20" s="21" t="n"/>
@@ -2713,30 +2711,31 @@
         </is>
       </c>
       <c r="C21" s="55" t="n">
-        <v>0.7916666666666666</v>
+        <v>0.6944444444444444</v>
       </c>
       <c r="D21" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E21" s="21" t="inlineStr">
         <is>
-          <t>עריכת שולחן: סלטי קייטרינג (סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס), חצי מהסלטים והחלות של שישי, צלחות וסכו"ם</t>
+          <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: כרעיים בגריל, אורז עם אטריות, אפונה וגזר, פלפל ממולא (טבעוני)
+חיבור המיחמים בפינת הקפה</t>
         </is>
       </c>
       <c r="F21" s="53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>שחר קרן, מאיה פקטר, עמית סיילס, אלה גוטליב</t>
+          <t>שילת פילפל, הילי אלפסי</t>
         </is>
       </c>
       <c r="H21" s="48" t="n"/>
       <c r="I21" s="48" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="J21" s="21" t="n"/>
@@ -2757,20 +2756,20 @@
       </c>
       <c r="D22" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E22" s="21" t="inlineStr">
         <is>
-          <t>הוצאת הגסטרונומים מתנור החימום</t>
+          <t>הוצאת הגסטרונומים של ארוחת הערב מתנור החימום לשולחן ההגשה</t>
         </is>
       </c>
       <c r="F22" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>שחר קרן, מאיה פקטר, עמית סיילס</t>
+          <t>שילת פילפל, הילי אלפסי</t>
         </is>
       </c>
       <c r="H22" s="48" t="n"/>
@@ -2787,36 +2786,36 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B23" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
+      <c r="B23" s="57" t="inlineStr">
+        <is>
+          <t>שבת</t>
         </is>
       </c>
       <c r="C23" s="55" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>פינוי הארוחה: האוכל שנשאר למקרר, צלחות וסכו"ם, וניגוב השולחנות</t>
+          <t>הכנסת האוכל של ארוחת הצהריים לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
         </is>
       </c>
       <c r="F23" s="53" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
+          <t>שילת פילפל, הילי אלפסי</t>
         </is>
       </c>
       <c r="H23" s="48" t="n"/>
       <c r="I23" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="J23" s="21" t="n"/>
@@ -2827,32 +2826,36 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B24" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C24" s="55" t="n"/>
+      <c r="B24" s="57" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C24" s="55" t="n">
+        <v>0.5520833333333334</v>
+      </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>שטיפת הגסטרונומים בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="F24" s="53" t="n"/>
+          <t>הוצאת הגסטרונומים של ארוחת הצהריים מתנור החימום לשולחן ההגשה</t>
+        </is>
+      </c>
+      <c r="F24" s="53" t="n">
+        <v>2</v>
+      </c>
       <c r="G24" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
+          <t>שילת פילפל, הילי אלפסי</t>
         </is>
       </c>
       <c r="H24" s="48" t="n"/>
       <c r="I24" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J24" s="21" t="n"/>
@@ -2869,35 +2872,39 @@
         </is>
       </c>
       <c r="C25" s="55" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.78125</v>
       </c>
       <c r="D25" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E25" s="21" t="inlineStr">
         <is>
-          <t>חימום העוגות — הכל פרווה</t>
+          <t>הכנת סלט כרוב מרענן, סלט טחינה ביתית</t>
         </is>
       </c>
       <c r="F25" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>ארבל פרנקו, ינון לוי</t>
-        </is>
-      </c>
-      <c r="H25" s="48" t="n"/>
+          <t>יונתן לירז, מעיין יוספי, ניתאי שלום</t>
+        </is>
+      </c>
+      <c r="H25" s="48" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
+        </is>
+      </c>
       <c r="I25" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="J25" s="21" t="n"/>
     </row>
-    <row r="26" ht="30" customHeight="1">
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -2909,35 +2916,38 @@
         </is>
       </c>
       <c r="C26" s="55" t="n">
-        <v>0.8541666666666666</v>
+        <v>0.7916666666666666</v>
       </c>
       <c r="D26" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E26" s="21" t="inlineStr">
         <is>
-          <t>חיתוך 10 תפוחים</t>
+          <t>עריכת השולחן:
+סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס
+חצי מהמטבוחה, חצי מסלט החצילים וחצי מהחלות
+צלחות וסכו"ם</t>
         </is>
       </c>
       <c r="F26" s="53" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G26" s="31" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>ינון לוי, יונתן לירז, מעיין יוספי, ניתאי שלום</t>
         </is>
       </c>
       <c r="H26" s="48" t="n"/>
       <c r="I26" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="J26" s="21" t="n"/>
     </row>
-    <row r="27" ht="30" customHeight="1">
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -2949,24 +2959,29 @@
         </is>
       </c>
       <c r="C27" s="55" t="n">
-        <v>0.875</v>
+        <v>0.8541666666666666</v>
       </c>
       <c r="D27" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E27" s="21" t="inlineStr">
         <is>
-          <t>פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
+          <t>פינוי הארוחה:
+האוכל שנשאר — למקרר
+צלחות וסכו"ם
+ניגוב השולחנות
+ניקוי הפחים
+טאטוא</t>
         </is>
       </c>
       <c r="F27" s="53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, רותם דרור, ארבל פרנקו</t>
+          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="H27" s="48" t="n"/>
@@ -2988,25 +3003,21 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C28" s="55" t="n">
-        <v>0.875</v>
-      </c>
+      <c r="C28" s="55" t="n"/>
       <c r="D28" s="48" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E28" s="21" t="inlineStr">
         <is>
-          <t>סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב</t>
-        </is>
-      </c>
-      <c r="F28" s="53" t="n">
-        <v>2</v>
-      </c>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F28" s="53" t="n"/>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>ינון לוי, נועם ישראל קומפאס</t>
+          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="H28" s="48" t="n"/>
@@ -3017,7 +3028,7 @@
       </c>
       <c r="J28" s="21" t="n"/>
     </row>
-    <row r="29" ht="30" customHeight="1">
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -3028,7 +3039,9 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C29" s="55" t="n"/>
+      <c r="C29" s="55" t="n">
+        <v>0.8541666666666666</v>
+      </c>
       <c r="D29" s="48" t="inlineStr">
         <is>
           <t>טיש</t>
@@ -3036,13 +3049,18 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="F29" s="53" t="n"/>
+          <t>חימום העוגות — הכל פרווה
+חיתוך 10 תפוחים
+סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב
+פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
+        </is>
+      </c>
+      <c r="F29" s="53" t="n">
+        <v>3</v>
+      </c>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>ארבל פרנקו, ינון לוי, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
+          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
         </is>
       </c>
       <c r="H29" s="48" t="n"/>
@@ -3059,41 +3077,37 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B30" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C30" s="55" t="n">
-        <v>0.4375</v>
-      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="n"/>
       <c r="D30" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E30" s="21" t="inlineStr">
         <is>
-          <t>סידור וניקיון פינת קפה — להוציא חלב, למלא קפה וסוכר</t>
-        </is>
-      </c>
-      <c r="F30" s="53" t="n">
-        <v>1</v>
-      </c>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F30" s="53" t="n"/>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
         </is>
       </c>
       <c r="H30" s="48" t="n"/>
       <c r="I30" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="J30" s="21" t="n"/>
     </row>
-    <row r="31" ht="30" customHeight="1">
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -3114,15 +3128,19 @@
       </c>
       <c r="E31" s="21" t="inlineStr">
         <is>
-          <t>חימום העוגות</t>
+          <t>סידור וניקיון פינת הקפה — להוציא חלב, למלא קפה וסוכר
+חימום העוגות
+הוצאת העוגות
+הוצאת חלב, קורנפלקס וחצי מהענבים
+טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
       </c>
       <c r="F31" s="53" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G31" s="31" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>ניצן גמלא, הלל פינגולד, אלרואי גרינברג</t>
         </is>
       </c>
       <c r="H31" s="48" t="n"/>
@@ -3133,7 +3151,7 @@
       </c>
       <c r="J31" s="21" t="n"/>
     </row>
-    <row r="32" ht="30" customHeight="1">
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -3145,30 +3163,37 @@
         </is>
       </c>
       <c r="C32" s="55" t="n">
-        <v>0.4375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="D32" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E32" s="21" t="inlineStr">
         <is>
-          <t>טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
+          <t>עריכת השולחן:
+הכנת סלט כרוב מרענן, סלט טחינה ביתית
+הוצאת שאר המטבוחה, סלט החצילים והחלות
+סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס</t>
         </is>
       </c>
       <c r="F32" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז</t>
-        </is>
-      </c>
-      <c r="H32" s="48" t="n"/>
+          <t>בניה מעוז, רגב שהם</t>
+        </is>
+      </c>
+      <c r="H32" s="48" t="inlineStr">
+        <is>
+          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
+        </is>
+      </c>
       <c r="I32" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J32" s="21" t="n"/>
@@ -3185,35 +3210,36 @@
         </is>
       </c>
       <c r="C33" s="55" t="n">
-        <v>0.4375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="D33" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E33" s="21" t="inlineStr">
         <is>
-          <t>הוצאת העוגות</t>
+          <t>כפות הגשה, צלחות וסכו"ם
+סידור שולחנות וכיסאות</t>
         </is>
       </c>
       <c r="F33" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>מעיין רחל דינר, הדר עמדי</t>
         </is>
       </c>
       <c r="H33" s="48" t="n"/>
       <c r="I33" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J33" s="21" t="n"/>
     </row>
-    <row r="34" ht="30" customHeight="1">
+    <row r="34" ht="90" customHeight="1">
       <c r="A34" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -3225,30 +3251,35 @@
         </is>
       </c>
       <c r="C34" s="55" t="n">
-        <v>0.4375</v>
+        <v>0.5833333333333334</v>
       </c>
       <c r="D34" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E34" s="21" t="inlineStr">
         <is>
-          <t>הוצאת חלב, קורנפלקס וחצי מהענבים</t>
+          <t>פינוי השולחנות:
+האוכל שנשאר — למקרר
+צלחות וסכו"ם
+ניקוי השולחנות
+ניקוי הפחים
+טאטוא</t>
         </is>
       </c>
       <c r="F34" s="53" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G34" s="31" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
         </is>
       </c>
       <c r="H34" s="48" t="n"/>
       <c r="I34" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J34" s="21" t="n"/>
@@ -3264,31 +3295,27 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C35" s="55" t="n">
-        <v>0.4583333333333333</v>
-      </c>
+      <c r="C35" s="55" t="n"/>
       <c r="D35" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E35" s="21" t="inlineStr">
         <is>
-          <t>הכנסת האוכל לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
-        </is>
-      </c>
-      <c r="F35" s="53" t="n">
-        <v>2</v>
-      </c>
+          <t>שטיפת הגסטרונומים בסיום הארוחה</t>
+        </is>
+      </c>
+      <c r="F35" s="53" t="n"/>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>הדר עמדי, רוני כהן</t>
+          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
         </is>
       </c>
       <c r="H35" s="48" t="n"/>
       <c r="I35" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J35" s="21" t="n"/>
@@ -3305,16 +3332,16 @@
         </is>
       </c>
       <c r="C36" s="55" t="n">
-        <v>0.5208333333333334</v>
+        <v>0.71875</v>
       </c>
       <c r="D36" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>עריכת השולחן: הכנת סלט כרוב מרענן, סלט טחינה ביתית, והוצאת שאר הסלטים של שישי, סלטי קייטרינג (סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס) וחלות</t>
+          <t>הוצאת העוגות לסעודה שלישית</t>
         </is>
       </c>
       <c r="F36" s="53" t="n">
@@ -3322,17 +3349,13 @@
       </c>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, אחיה נחמני</t>
-        </is>
-      </c>
-      <c r="H36" s="48" t="inlineStr">
-        <is>
-          <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
-        </is>
-      </c>
+          <t>רוני כהן, עמית שי אברהם</t>
+        </is>
+      </c>
+      <c r="H36" s="48" t="n"/>
       <c r="I36" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>סעודה שלישית</t>
         </is>
       </c>
       <c r="J36" s="21" t="n"/>
@@ -3340,233 +3363,130 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B37" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C37" s="55" t="n">
-        <v>0.5208333333333334</v>
-      </c>
+          <t>תורנות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="B37" s="56" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="n"/>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>פריסת האוכל, כפות הגשה, צלחות וסכו"ם, וסידור שולחנות וכיסאות</t>
+          <t>להחזיר את בית המדרש לקדמותו — השולחנות, הכסאות, המחיצה והסידורים, כמו לפני שבת</t>
         </is>
       </c>
       <c r="F37" s="53" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G37" s="31" t="inlineStr">
         <is>
-          <t>הדר עמדי, רוני כהן</t>
+          <t>ניתאי שלום, מעיין יוספי, יונתן לירז, משה אוברשטיין, אביה וייל, יערה ריס, שחר מרקוביץ' גליק, עמית סיילס, מאיה פקטר, שילת פילפל</t>
         </is>
       </c>
       <c r="H37" s="48" t="n"/>
       <c r="I37" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>ניקיונות מוצ"ש</t>
         </is>
       </c>
       <c r="J37" s="21" t="n"/>
     </row>
-    <row r="38" ht="30" customHeight="1">
+    <row r="38" ht="90" customHeight="1">
       <c r="A38" s="53" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B38" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C38" s="55" t="n">
-        <v>0.5833333333333334</v>
-      </c>
+          <t>תורנות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="B38" s="56" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="C38" s="55" t="n"/>
       <c r="D38" s="48" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E38" s="21" t="inlineStr">
         <is>
-          <t>פינוי השולחנות: האוכל שנשאר למקרר, צלחות וסכו"ם, וניגוב השולחנות</t>
+          <t>שטיפת הגסטרונומים
+שטיפת הרצפה
+ניקוי המטבח
+ניקוי חדר המקררים
+זריקת הפחים
+פינוי התנורים</t>
         </is>
       </c>
       <c r="F38" s="53" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G38" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
+          <t>רועי צבי סרי, נגה שוהם, ינון לוי, נדב טוקר, הילי אלפסי, אחיה נחמני, ארבל פרנקו, חיים שמאי, אלה גוטליב, זואי כהן, יואב אוחנה, שחר קרן</t>
         </is>
       </c>
       <c r="H38" s="48" t="n"/>
       <c r="I38" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>ניקיונות מוצ"ש</t>
         </is>
       </c>
       <c r="J38" s="21" t="n"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B39" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
+    <row r="39" ht="18" customHeight="1">
+      <c r="A39" s="53" t="n"/>
+      <c r="B39" s="53" t="n"/>
       <c r="C39" s="55" t="n"/>
-      <c r="D39" s="48" t="inlineStr">
-        <is>
-          <t>פינוי ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="E39" s="21" t="inlineStr">
-        <is>
-          <t>שטיפת הגסטרונומים בסיום הארוחה</t>
-        </is>
-      </c>
+      <c r="D39" s="48" t="n"/>
+      <c r="E39" s="21" t="n"/>
       <c r="F39" s="53" t="n"/>
-      <c r="G39" s="31" t="inlineStr">
-        <is>
-          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
-        </is>
-      </c>
+      <c r="G39" s="31" t="n"/>
       <c r="H39" s="48" t="n"/>
-      <c r="I39" s="48" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
+      <c r="I39" s="48" t="n"/>
       <c r="J39" s="21" t="n"/>
     </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B40" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C40" s="55" t="n">
-        <v>0.71875</v>
-      </c>
-      <c r="D40" s="48" t="inlineStr">
-        <is>
-          <t>פינוי ארוחת צהריים שבת</t>
-        </is>
-      </c>
-      <c r="E40" s="21" t="inlineStr">
-        <is>
-          <t>הוצאת העוגות לסעודה שלישית</t>
-        </is>
-      </c>
-      <c r="F40" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G40" s="31" t="inlineStr">
-        <is>
-          <t>שירה ספונוב, קובי סמייסון</t>
-        </is>
-      </c>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="53" t="n"/>
+      <c r="B40" s="53" t="n"/>
+      <c r="C40" s="55" t="n"/>
+      <c r="D40" s="48" t="n"/>
+      <c r="E40" s="21" t="n"/>
+      <c r="F40" s="53" t="n"/>
+      <c r="G40" s="31" t="n"/>
       <c r="H40" s="48" t="n"/>
-      <c r="I40" s="48" t="inlineStr">
-        <is>
-          <t>סעודה שלישית</t>
-        </is>
-      </c>
+      <c r="I40" s="48" t="n"/>
       <c r="J40" s="21" t="n"/>
     </row>
-    <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="53" t="inlineStr">
-        <is>
-          <t>תורנות מוצ"ש</t>
-        </is>
-      </c>
-      <c r="B41" s="56" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
+    <row r="41" ht="18" customHeight="1">
+      <c r="A41" s="53" t="n"/>
+      <c r="B41" s="53" t="n"/>
       <c r="C41" s="55" t="n"/>
-      <c r="D41" s="48" t="inlineStr">
-        <is>
-          <t>ניקיון בית המדרש</t>
-        </is>
-      </c>
-      <c r="E41" s="21" t="inlineStr">
-        <is>
-          <t>ניקיון בית המדרש</t>
-        </is>
-      </c>
-      <c r="F41" s="53" t="n">
-        <v>12</v>
-      </c>
-      <c r="G41" s="31" t="inlineStr">
-        <is>
-          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, ארבל פרנקו, ינון לוי, אביה וייל, יואב אוחנה, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
-        </is>
-      </c>
+      <c r="D41" s="48" t="n"/>
+      <c r="E41" s="21" t="n"/>
+      <c r="F41" s="53" t="n"/>
+      <c r="G41" s="31" t="n"/>
       <c r="H41" s="48" t="n"/>
-      <c r="I41" s="48" t="inlineStr">
-        <is>
-          <t>ניקיונות מוצ"ש</t>
-        </is>
-      </c>
+      <c r="I41" s="48" t="n"/>
       <c r="J41" s="21" t="n"/>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="53" t="inlineStr">
-        <is>
-          <t>תורנות מוצ"ש</t>
-        </is>
-      </c>
-      <c r="B42" s="56" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
+    <row r="42" ht="18" customHeight="1">
+      <c r="A42" s="53" t="n"/>
+      <c r="B42" s="53" t="n"/>
       <c r="C42" s="55" t="n"/>
-      <c r="D42" s="48" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל</t>
-        </is>
-      </c>
-      <c r="E42" s="21" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל</t>
-        </is>
-      </c>
-      <c r="F42" s="53" t="n">
-        <v>12</v>
-      </c>
-      <c r="G42" s="31" t="inlineStr">
-        <is>
-          <t>רועי צבי סרי, יהב לוי, יובל יצחק, הילי אלפסי, שילת פילפל, רוני פרנקל, אנה עזריאל, טליה קור, של״ו רובינשטיין, איתי בן מנחם, אלה מאיר, שחר מרקוביץ' גליק</t>
-        </is>
-      </c>
+      <c r="D42" s="48" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="53" t="n"/>
+      <c r="G42" s="31" t="n"/>
       <c r="H42" s="48" t="n"/>
-      <c r="I42" s="48" t="inlineStr">
-        <is>
-          <t>ניקיונות מוצ"ש</t>
-        </is>
-      </c>
+      <c r="I42" s="48" t="n"/>
       <c r="J42" s="21" t="n"/>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -4533,7 +4453,7 @@
     <row r="124" ht="28" customHeight="1">
       <c r="A124" s="26" t="inlineStr">
         <is>
-          <t>«אנשים» = כמה צריך למשימה; ריק = כל הקבוצה. «שמות» מתמלא ע"י השיבוץ ואפשר לתקן ידנית. «מתכון» = מנה מ«מתכונים»; כמה מנות מופרדות ב-; (משימה שמכינה שני סלטים). «עוגן» = האירוע בלו"ז שלידו המשימה תופיע בלו"ז הצל. הניקוד יושב ב«קבוצות».</t>
+          <t>«אנשים» = כמה צריך למשימה; ריק = כל הקבוצה. «שמות» מתמלא ע"י השיבוץ ואפשר לתקן ידנית. «מתכון» = מנה מ«מתכונים»; כמה מנות מופרדות ב-; (משימה שמכינה שני סלטים). «עוגן» = האירוע בלו"ז שהמשימה קשורה אליו (ממנו השעה היחסית). הניקוד יושב ב«קבוצות».</t>
         </is>
       </c>
     </row>
@@ -4648,7 +4568,7 @@
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד, בניה מעוז</t>
+          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד</t>
         </is>
       </c>
       <c r="F3" s="50">
@@ -4676,14 +4596,10 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
-        <is>
-          <t>רוני כהן, מעיין רחל דינר, הדר עמדי</t>
-        </is>
-      </c>
+          <t>אלה מאיר</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="n"/>
       <c r="F4" s="50">
         <f>IF(E4="","",LEN(E4)-LEN(SUBSTITUTE(E4,",",""))+1)</f>
         <v/>
@@ -4709,12 +4625,12 @@
       </c>
       <c r="D5" s="34" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>זואי כהן, עמית סיילס, שחר קרן, עמית שי אברהם</t>
+          <t>בניה מעוז, רוני כהן</t>
         </is>
       </c>
       <c r="F5" s="50">
@@ -4742,12 +4658,12 @@
       </c>
       <c r="D6" s="34" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, אחיה נחמני, אלה גוטליב, מאיה פקטר</t>
+          <t>מעיין רחל דינר, הדר עמדי, זואי כהן</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -4775,12 +4691,12 @@
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>קובי סמייסון, יערה ריס, נבו בלוך, איתי בן מנחם</t>
+          <t>עמית סיילס, שחר קרן, עמית שי אברהם, שירה ספונוב</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -4811,11 +4727,7 @@
           <t>איתן כהן</t>
         </is>
       </c>
-      <c r="E8" s="31" t="inlineStr">
-        <is>
-          <t>איתן כהן, יהב לוי</t>
-        </is>
-      </c>
+      <c r="E8" s="31" t="n"/>
       <c r="F8" s="50">
         <f>IF(E8="","",LEN(E8)-LEN(SUBSTITUTE(E8,",",""))+1)</f>
         <v/>
@@ -4841,12 +4753,12 @@
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, תמר פרימור, רועי צבי סרי, עופר בביוף</t>
+          <t>אחיה נחמני, אלה גוטליב</t>
         </is>
       </c>
       <c r="F9" s="50">
@@ -4874,12 +4786,12 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="E10" s="31" t="inlineStr">
         <is>
-          <t>נגה חוה כהן, ירדן בן שחר, טליה קור, יובל יצחק</t>
+          <t>מאיה פקטר, קובי סמייסון, יערה ריס, נבו בלוך</t>
         </is>
       </c>
       <c r="F10" s="50">
@@ -4912,7 +4824,7 @@
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>אוריה תעשה, משה אוברשטיין, הילה לביא, שילת פילפל, תמר פרידמן, שחר מרקוביץ' גליק, אנה עזריאל, נועם ישראל קומפאס, של״ו רובינשטיין, רוני פרנקל, כליל בלאוקופף, הילי אלפסי</t>
+          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן, אלה מאיר, אנה עזריאל, איתי בן מנחם, רוני פרנקל, תמר פרימור, יובל יצחק, איתן כהן</t>
         </is>
       </c>
       <c r="F11" s="50">
@@ -4940,12 +4852,12 @@
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>נגה שוהם, נדב טוקר, איתמר אסנהיים, איתן וינסטון, חיים שמאי, שי- לי וולגמוט, הילה עזרא</t>
+          <t>נועם ישראל קומפאס, של״ו רובינשטיין, יהב לוי, נגה חוה כהן, ירדן בן שחר, כליל בלאוקופף, עופר בביוף</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -4960,7 +4872,7 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="47" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="B13" s="53" t="inlineStr">
@@ -4973,12 +4885,12 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>אלה גוטליב, שחר קרן, מאיה פקטר, עמית סיילס</t>
+          <t>שילת פילפל, הילי אלפסי</t>
         </is>
       </c>
       <c r="F13" s="50">
@@ -4993,7 +4905,7 @@
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="47" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="B14" s="53" t="inlineStr">
@@ -5011,7 +4923,7 @@
       </c>
       <c r="E14" s="31" t="inlineStr">
         <is>
-          <t>מעיין יוספי, יונתן לירז, ניתאי שלום, אביה וייל, יואב אוחנה</t>
+          <t>יונתן לירז, מעיין יוספי, ניתאי שלום, ינון לוי</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5026,7 +4938,7 @@
     <row r="15" ht="30" customHeight="1">
       <c r="A15" s="47" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="B15" s="53" t="inlineStr">
@@ -5035,16 +4947,16 @@
         </is>
       </c>
       <c r="C15" s="53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="34" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>ארבל פרנקו, ינון לוי, נועם ישראל קומפאס, אוריה תעשה, רותם דרור</t>
+          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -5059,7 +4971,7 @@
     <row r="16" ht="30" customHeight="1">
       <c r="A16" s="47" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="B16" s="53" t="inlineStr">
@@ -5072,12 +4984,12 @@
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="E16" s="31" t="inlineStr">
         <is>
-          <t>ניצן גמלא, הלל פינגולד, בניה מעוז, אלרואי גרינברג, רגב שהם</t>
+          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
         </is>
       </c>
       <c r="F16" s="50">
@@ -5092,7 +5004,7 @@
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="47" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="B17" s="53" t="inlineStr">
@@ -5101,16 +5013,16 @@
         </is>
       </c>
       <c r="C17" s="53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>הדר עמדי, רוני כהן, מעיין רחל דינר, אחיה נחמני</t>
+          <t>ניצן גמלא, הלל פינגולד, אלרואי גרינברג</t>
         </is>
       </c>
       <c r="F17" s="50">
@@ -5125,7 +5037,7 @@
     <row r="18" ht="30" customHeight="1">
       <c r="A18" s="47" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="B18" s="53" t="inlineStr">
@@ -5138,12 +5050,12 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, קובי סמייסון, זואי כהן, עמית שי אברהם, יערה ריס</t>
+          <t>בניה מעוז, רגב שהם, מעיין רחל דינר, הדר עמדי</t>
         </is>
       </c>
       <c r="F18" s="50">
@@ -5158,12 +5070,12 @@
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="47" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="B19" s="53" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="C19" s="53" t="n">
@@ -5171,12 +5083,12 @@
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, ניתאי שלום, מעיין יוספי, ארבל פרנקו, ינון לוי, אביה וייל, יואב אוחנה, תמר פרידמן, תמר פרימור, נבו בלוך, נגה חוה כהן, הילה לביא</t>
+          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -5191,7 +5103,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="47" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="B20" s="53" t="inlineStr">
@@ -5200,16 +5112,16 @@
         </is>
       </c>
       <c r="C20" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>רועי צבי סרי, יהב לוי, יובל יצחק, הילי אלפסי, שילת פילפל, רוני פרנקל, אנה עזריאל, טליה קור, של״ו רובינשטיין, איתי בן מנחם, אלה מאיר, שחר מרקוביץ' גליק</t>
+          <t>ניתאי שלום, מעיין יוספי, יונתן לירז, משה אוברשטיין, אביה וייל, יערה ריס, שחר מרקוביץ' גליק, עמית סיילס, מאיה פקטר, שילת פילפל</t>
         </is>
       </c>
       <c r="F20" s="50">
@@ -5224,7 +5136,7 @@
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="47" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="B21" s="53" t="inlineStr">
@@ -5237,12 +5149,12 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, עופר בביוף, ירדן בן שחר, איתן כהן, כליל בלאוקופף</t>
+          <t>רועי צבי סרי, נגה שוהם, ינון לוי, נדב טוקר, הילי אלפסי, אחיה נחמני, ארבל פרנקו, חיים שמאי, אלה גוטליב, זואי כהן, יואב אוחנה, שחר קרן</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -5254,12 +5166,30 @@
         <v/>
       </c>
     </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="47" t="n"/>
-      <c r="B22" s="53" t="n"/>
-      <c r="C22" s="53" t="n"/>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="31" t="n"/>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="47" t="inlineStr">
+        <is>
+          <t>ארוחת ערב מוצ"ש</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>תורנות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="C22" s="53" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" s="34" t="inlineStr">
+        <is>
+          <t>רותם דרור</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>שירה ספונוב, ירדן בן שחר, רותם דרור, תמר פרידמן, איתן כהן</t>
+        </is>
+      </c>
       <c r="F22" s="50">
         <f>IF(E22="","",LEN(E22)-LEN(SUBSTITUTE(E22,",",""))+1)</f>
         <v/>
@@ -5539,7 +5469,7 @@
       </c>
       <c r="E3" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F3" s="50">
@@ -5578,7 +5508,7 @@
       </c>
       <c r="E4" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F4" s="50">
@@ -5586,7 +5516,7 @@
         <v/>
       </c>
       <c r="G4" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H4" s="50">
         <f>IF(A4="","",SUMIF('היסטוריה'!$B$3:$B$3002,A4,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5617,7 +5547,7 @@
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F5" s="50">
@@ -5625,7 +5555,7 @@
         <v/>
       </c>
       <c r="G5" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H5" s="50">
         <f>IF(A5="","",SUMIF('היסטוריה'!$B$3:$B$3002,A5,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5656,7 +5586,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>גסטרונומים; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -5664,7 +5594,7 @@
         <v/>
       </c>
       <c r="G6" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="50">
         <f>IF(A6="","",SUMIF('היסטוריה'!$B$3:$B$3002,A6,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5695,7 +5625,7 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>סלט חצילים; ניקיון חדר האוכל</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -5703,7 +5633,7 @@
         <v/>
       </c>
       <c r="G7" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H7" s="50">
         <f>IF(A7="","",SUMIF('היסטוריה'!$B$3:$B$3002,A7,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5734,7 +5664,7 @@
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; הכנת ארוחת ערב</t>
+          <t>מטבוחה; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F8" s="50">
@@ -5742,7 +5672,7 @@
         <v/>
       </c>
       <c r="G8" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H8" s="50">
         <f>IF(A8="","",SUMIF('היסטוריה'!$B$3:$B$3002,A8,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5773,7 +5703,7 @@
       </c>
       <c r="E9" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל בשישי; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F9" s="50">
@@ -5812,7 +5742,7 @@
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; הכנת ארוחת צהריים שבת</t>
+          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F10" s="50">
@@ -5820,7 +5750,7 @@
         <v/>
       </c>
       <c r="G10" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H10" s="50">
         <f>IF(A10="","",SUMIF('היסטוריה'!$B$3:$B$3002,A10,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5851,7 +5781,7 @@
       </c>
       <c r="E11" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F11" s="50">
@@ -5890,7 +5820,7 @@
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; הכנת ארוחת ערב</t>
+          <t>מטבוחה; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -5958,7 +5888,7 @@
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
+          <t>טיש; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5966,7 +5896,7 @@
         <v/>
       </c>
       <c r="G14" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H14" s="50">
         <f>IF(A14="","",SUMIF('היסטוריה'!$B$3:$B$3002,A14,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5997,7 +5927,7 @@
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; טיש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -6005,7 +5935,7 @@
         <v/>
       </c>
       <c r="G15" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H15" s="50">
         <f>IF(A15="","",SUMIF('היסטוריה'!$B$3:$B$3002,A15,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6036,7 +5966,7 @@
       </c>
       <c r="E16" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F16" s="50">
@@ -6104,7 +6034,7 @@
       </c>
       <c r="E18" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>טיש; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F18" s="50">
@@ -6112,7 +6042,7 @@
         <v/>
       </c>
       <c r="G18" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="50">
         <f>IF(A18="","",SUMIF('היסטוריה'!$B$3:$B$3002,A18,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6143,7 +6073,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -6182,7 +6112,7 @@
       </c>
       <c r="E20" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F20" s="50">
@@ -6190,7 +6120,7 @@
         <v/>
       </c>
       <c r="G20" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="50">
         <f>IF(A20="","",SUMIF('היסטוריה'!$B$3:$B$3002,A20,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6221,7 +6151,7 @@
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -6229,7 +6159,7 @@
         <v/>
       </c>
       <c r="G21" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H21" s="50">
         <f>IF(A21="","",SUMIF('היסטוריה'!$B$3:$B$3002,A21,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6258,18 +6188,12 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E22" s="34" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
+      <c r="E22" s="34" t="n"/>
       <c r="F22" s="50">
         <f>IF(A22="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A22&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G22" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="G22" s="35" t="n"/>
       <c r="H22" s="50">
         <f>IF(A22="","",SUMIF('היסטוריה'!$B$3:$B$3002,A22,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -6295,7 +6219,7 @@
       </c>
       <c r="E23" s="34" t="inlineStr">
         <is>
-          <t>חלות; קידוש</t>
+          <t>עוגת שוקולד; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F23" s="50">
@@ -6303,7 +6227,7 @@
         <v/>
       </c>
       <c r="G23" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="50">
         <f>IF(A23="","",SUMIF('היסטוריה'!$B$3:$B$3002,A23,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6330,7 +6254,7 @@
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F24" s="50">
@@ -6338,7 +6262,7 @@
         <v/>
       </c>
       <c r="G24" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H24" s="50">
         <f>IF(A24="","",SUMIF('היסטוריה'!$B$3:$B$3002,A24,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6369,7 +6293,7 @@
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F25" s="50">
@@ -6408,7 +6332,7 @@
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F26" s="50">
@@ -6416,7 +6340,7 @@
         <v/>
       </c>
       <c r="G26" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H26" s="50">
         <f>IF(A26="","",SUMIF('היסטוריה'!$B$3:$B$3002,A26,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6486,7 +6410,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; הכנת ארוחת ערב</t>
+          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F28" s="50">
@@ -6494,7 +6418,7 @@
         <v/>
       </c>
       <c r="G28" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="50">
         <f>IF(A28="","",SUMIF('היסטוריה'!$B$3:$B$3002,A28,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6525,7 +6449,7 @@
       </c>
       <c r="E29" s="34" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F29" s="50">
@@ -6533,7 +6457,7 @@
         <v/>
       </c>
       <c r="G29" s="35" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H29" s="50">
         <f>IF(A29="","",SUMIF('היסטוריה'!$B$3:$B$3002,A29,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6622,7 +6546,7 @@
       </c>
       <c r="E32" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; פינוי ארוחת צהריים שבת</t>
+          <t>מטבוחה; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F32" s="50">
@@ -6630,7 +6554,7 @@
         <v/>
       </c>
       <c r="G32" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H32" s="50">
         <f>IF(A32="","",SUMIF('היסטוריה'!$B$3:$B$3002,A32,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6700,7 +6624,7 @@
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F34" s="50">
@@ -6768,7 +6692,7 @@
       </c>
       <c r="E36" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F36" s="50">
@@ -6776,7 +6700,7 @@
         <v/>
       </c>
       <c r="G36" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H36" s="50">
         <f>IF(A36="","",SUMIF('היסטוריה'!$B$3:$B$3002,A36,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6803,7 +6727,7 @@
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; פינוי ארוחת צהריים שבת</t>
+          <t>ארוחת צהריים שישי; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F37" s="50">
@@ -6842,7 +6766,7 @@
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>טיש; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F38" s="50">
@@ -6850,7 +6774,7 @@
         <v/>
       </c>
       <c r="G38" s="35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H38" s="50">
         <f>IF(A38="","",SUMIF('היסטוריה'!$B$3:$B$3002,A38,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6881,7 +6805,7 @@
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון בית המדרש</t>
+          <t>ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F39" s="50">
@@ -6889,7 +6813,7 @@
         <v/>
       </c>
       <c r="G39" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H39" s="50">
         <f>IF(A39="","",SUMIF('היסטוריה'!$B$3:$B$3002,A39,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6920,7 +6844,7 @@
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F40" s="50">
@@ -6928,7 +6852,7 @@
         <v/>
       </c>
       <c r="G40" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H40" s="50">
         <f>IF(A40="","",SUMIF('היסטוריה'!$B$3:$B$3002,A40,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6959,7 +6883,7 @@
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; פינוי ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F41" s="50">
@@ -6967,7 +6891,7 @@
         <v/>
       </c>
       <c r="G41" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H41" s="50">
         <f>IF(A41="","",SUMIF('היסטוריה'!$B$3:$B$3002,A41,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6998,7 +6922,7 @@
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F42" s="50">
@@ -7006,7 +6930,7 @@
         <v/>
       </c>
       <c r="G42" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H42" s="50">
         <f>IF(A42="","",SUMIF('היסטוריה'!$B$3:$B$3002,A42,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7037,7 +6961,7 @@
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F43" s="50">
@@ -7045,7 +6969,7 @@
         <v/>
       </c>
       <c r="G43" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H43" s="50">
         <f>IF(A43="","",SUMIF('היסטוריה'!$B$3:$B$3002,A43,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7076,7 +7000,7 @@
       </c>
       <c r="E44" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F44" s="50">
@@ -7084,7 +7008,7 @@
         <v/>
       </c>
       <c r="G44" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H44" s="50">
         <f>IF(A44="","",SUMIF('היסטוריה'!$B$3:$B$3002,A44,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7144,7 +7068,7 @@
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון בית המדרש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F46" s="50">
@@ -7152,7 +7076,7 @@
         <v/>
       </c>
       <c r="G46" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H46" s="50">
         <f>IF(A46="","",SUMIF('היסטוריה'!$B$3:$B$3002,A46,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7183,7 +7107,7 @@
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; פינוי ארוחת צהריים שבת</t>
+          <t>מטבוחה; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F47" s="50">
@@ -7222,7 +7146,7 @@
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון בית המדרש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F48" s="50">
@@ -7230,7 +7154,7 @@
         <v/>
       </c>
       <c r="G48" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H48" s="50">
         <f>IF(A48="","",SUMIF('היסטוריה'!$B$3:$B$3002,A48,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7261,7 +7185,7 @@
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ניקיון בית המדרש</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="F49" s="50">
@@ -7269,7 +7193,7 @@
         <v/>
       </c>
       <c r="G49" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H49" s="50">
         <f>IF(A49="","",SUMIF('היסטוריה'!$B$3:$B$3002,A49,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7300,7 +7224,7 @@
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F50" s="50">
@@ -7308,7 +7232,7 @@
         <v/>
       </c>
       <c r="G50" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H50" s="50">
         <f>IF(A50="","",SUMIF('היסטוריה'!$B$3:$B$3002,A50,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7368,7 +7292,7 @@
       </c>
       <c r="E52" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון בית המדרש</t>
+          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F52" s="50">
@@ -7376,7 +7300,7 @@
         <v/>
       </c>
       <c r="G52" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H52" s="50">
         <f>IF(A52="","",SUMIF('היסטוריה'!$B$3:$B$3002,A52,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7436,7 +7360,7 @@
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F54" s="50">
@@ -7444,7 +7368,7 @@
         <v/>
       </c>
       <c r="G54" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H54" s="50">
         <f>IF(A54="","",SUMIF('היסטוריה'!$B$3:$B$3002,A54,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7473,18 +7397,12 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E55" s="34" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
+      <c r="E55" s="34" t="n"/>
       <c r="F55" s="50">
         <f>IF(A55="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A55&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G55" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="G55" s="35" t="n"/>
       <c r="H55" s="50">
         <f>IF(A55="","",SUMIF('היסטוריה'!$B$3:$B$3002,A55,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -7514,7 +7432,7 @@
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ניקיון חדר האוכל</t>
+          <t>גסטרונומים; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F56" s="50">
@@ -7522,7 +7440,7 @@
         <v/>
       </c>
       <c r="G56" s="35" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H56" s="50">
         <f>IF(A56="","",SUMIF('היסטוריה'!$B$3:$B$3002,A56,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7553,7 +7471,7 @@
       </c>
       <c r="E57" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; טיש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F57" s="50">
@@ -7561,7 +7479,7 @@
         <v/>
       </c>
       <c r="G57" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H57" s="50">
         <f>IF(A57="","",SUMIF('היסטוריה'!$B$3:$B$3002,A57,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7592,7 +7510,7 @@
       </c>
       <c r="E58" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל</t>
+          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F58" s="50">
@@ -7600,7 +7518,7 @@
         <v/>
       </c>
       <c r="G58" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H58" s="50">
         <f>IF(A58="","",SUMIF('היסטוריה'!$B$3:$B$3002,A58,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7631,7 +7549,7 @@
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>סלט חצילים; ארוחת ערב מוצ"ש</t>
+          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F59" s="50">
@@ -7670,7 +7588,7 @@
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F60" s="50">
@@ -7678,7 +7596,7 @@
         <v/>
       </c>
       <c r="G60" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H60" s="50">
         <f>IF(A60="","",SUMIF('היסטוריה'!$B$3:$B$3002,A60,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7709,7 +7627,7 @@
       </c>
       <c r="E61" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון חדר האוכל</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F61" s="50">
@@ -7717,7 +7635,7 @@
         <v/>
       </c>
       <c r="G61" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H61" s="50">
         <f>IF(A61="","",SUMIF('היסטוריה'!$B$3:$B$3002,A61,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7787,7 +7705,7 @@
       </c>
       <c r="E63" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F63" s="50">
@@ -7855,7 +7773,7 @@
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; פינוי ארוחת צהריים שבת</t>
+          <t>ארוחת צהריים שישי; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F65" s="50">
@@ -7981,7 +7899,7 @@
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; הכנת ארוחת ערב</t>
+          <t>ארוחת צהריים שישי; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F69" s="50">
@@ -8045,7 +7963,7 @@
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>חלות; קידוש</t>
+          <t>חלות; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F71" s="50">
@@ -8053,7 +7971,7 @@
         <v/>
       </c>
       <c r="G71" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H71" s="50">
         <f>IF(A71="","",SUMIF('היסטוריה'!$B$3:$B$3002,A71,'היסטוריה'!$E$3:$E$3002))</f>
@@ -8084,7 +8002,7 @@
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן; הכנת ארוחת צהריים שבת</t>
+          <t>עוגת שוקולד; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F72" s="50">
@@ -9150,7 +9068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F205"/>
+  <dimension ref="A1:F189"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -11431,7 +11349,7 @@
       </c>
       <c r="B100" s="59" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="C100" s="60" t="inlineStr">
@@ -11454,7 +11372,7 @@
       </c>
       <c r="B101" s="59" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C101" s="60" t="inlineStr">
@@ -11477,7 +11395,7 @@
       </c>
       <c r="B102" s="59" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>נבו בלוך</t>
         </is>
       </c>
       <c r="C102" s="60" t="inlineStr">
@@ -11500,7 +11418,7 @@
       </c>
       <c r="B103" s="59" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="C103" s="60" t="inlineStr">
@@ -11523,7 +11441,7 @@
       </c>
       <c r="B104" s="59" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C104" s="60" t="inlineStr">
@@ -11533,7 +11451,7 @@
       </c>
       <c r="D104" s="59" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E104" s="60" t="n">
@@ -11546,7 +11464,7 @@
       </c>
       <c r="B105" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C105" s="60" t="inlineStr">
@@ -11556,7 +11474,7 @@
       </c>
       <c r="D105" s="59" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E105" s="60" t="n">
@@ -11569,7 +11487,7 @@
       </c>
       <c r="B106" s="59" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="C106" s="60" t="inlineStr">
@@ -11579,7 +11497,7 @@
       </c>
       <c r="D106" s="59" t="inlineStr">
         <is>
-          <t>בראוניז ללא גלוטן</t>
+          <t>חלות</t>
         </is>
       </c>
       <c r="E106" s="60" t="n">
@@ -11592,7 +11510,7 @@
       </c>
       <c r="B107" s="59" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C107" s="60" t="inlineStr">
@@ -11615,7 +11533,7 @@
       </c>
       <c r="B108" s="59" t="inlineStr">
         <is>
-          <t>בניה מעוז</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C108" s="60" t="inlineStr">
@@ -11625,7 +11543,7 @@
       </c>
       <c r="D108" s="59" t="inlineStr">
         <is>
-          <t>חלות</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E108" s="60" t="n">
@@ -11638,7 +11556,7 @@
       </c>
       <c r="B109" s="59" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C109" s="60" t="inlineStr">
@@ -11648,7 +11566,7 @@
       </c>
       <c r="D109" s="59" t="inlineStr">
         <is>
-          <t>חלות</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E109" s="60" t="n">
@@ -11661,7 +11579,7 @@
       </c>
       <c r="B110" s="59" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>שחר קרן</t>
         </is>
       </c>
       <c r="C110" s="60" t="inlineStr">
@@ -11671,7 +11589,7 @@
       </c>
       <c r="D110" s="59" t="inlineStr">
         <is>
-          <t>חלות</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E110" s="60" t="n">
@@ -11684,7 +11602,7 @@
       </c>
       <c r="B111" s="59" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>שירה ספונוב</t>
         </is>
       </c>
       <c r="C111" s="60" t="inlineStr">
@@ -11694,7 +11612,7 @@
       </c>
       <c r="D111" s="59" t="inlineStr">
         <is>
-          <t>חלות</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E111" s="60" t="n">
@@ -11707,7 +11625,7 @@
       </c>
       <c r="B112" s="59" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C112" s="60" t="inlineStr">
@@ -11717,7 +11635,7 @@
       </c>
       <c r="D112" s="59" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E112" s="60" t="n">
@@ -11730,7 +11648,7 @@
       </c>
       <c r="B113" s="59" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C113" s="60" t="inlineStr">
@@ -11740,7 +11658,7 @@
       </c>
       <c r="D113" s="59" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E113" s="60" t="n">
@@ -11753,7 +11671,7 @@
       </c>
       <c r="B114" s="59" t="inlineStr">
         <is>
-          <t>נבו בלוך</t>
+          <t>בניה מעוז</t>
         </is>
       </c>
       <c r="C114" s="60" t="inlineStr">
@@ -11763,7 +11681,7 @@
       </c>
       <c r="D114" s="59" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>עוגת שוקולד</t>
         </is>
       </c>
       <c r="E114" s="60" t="n">
@@ -11776,7 +11694,7 @@
       </c>
       <c r="B115" s="59" t="inlineStr">
         <is>
-          <t>קובי סמייסון</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C115" s="60" t="inlineStr">
@@ -11786,7 +11704,7 @@
       </c>
       <c r="D115" s="59" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>עוגת שוקולד</t>
         </is>
       </c>
       <c r="E115" s="60" t="n">
@@ -11799,7 +11717,7 @@
       </c>
       <c r="B116" s="59" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C116" s="60" t="inlineStr">
@@ -11809,7 +11727,7 @@
       </c>
       <c r="D116" s="59" t="inlineStr">
         <is>
-          <t>סלט חצילים</t>
+          <t>עוגת שמרים</t>
         </is>
       </c>
       <c r="E116" s="60" t="n">
@@ -11822,7 +11740,7 @@
       </c>
       <c r="B117" s="59" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C117" s="60" t="inlineStr">
@@ -11832,7 +11750,7 @@
       </c>
       <c r="D117" s="59" t="inlineStr">
         <is>
-          <t>סלט חצילים</t>
+          <t>עוגת שמרים</t>
         </is>
       </c>
       <c r="E117" s="60" t="n">
@@ -11845,7 +11763,7 @@
       </c>
       <c r="B118" s="59" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C118" s="60" t="inlineStr">
@@ -11855,7 +11773,7 @@
       </c>
       <c r="D118" s="59" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>עוגת שמרים</t>
         </is>
       </c>
       <c r="E118" s="60" t="n">
@@ -11868,17 +11786,17 @@
       </c>
       <c r="B119" s="59" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C119" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D119" s="59" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E119" s="60" t="n">
@@ -11891,17 +11809,17 @@
       </c>
       <c r="B120" s="59" t="inlineStr">
         <is>
-          <t>רועי צבי סרי</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C120" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D120" s="59" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E120" s="60" t="n">
@@ -11914,17 +11832,17 @@
       </c>
       <c r="B121" s="59" t="inlineStr">
         <is>
-          <t>תמר פרימור</t>
+          <t>רותם דרור</t>
         </is>
       </c>
       <c r="C121" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D121" s="59" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E121" s="60" t="n">
@@ -11937,17 +11855,17 @@
       </c>
       <c r="B122" s="59" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>שירה ספונוב</t>
         </is>
       </c>
       <c r="C122" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D122" s="59" t="inlineStr">
         <is>
-          <t>עוגת שוקולד</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E122" s="60" t="n">
@@ -11960,17 +11878,17 @@
       </c>
       <c r="B123" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>תמר פרידמן</t>
         </is>
       </c>
       <c r="C123" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D123" s="59" t="inlineStr">
         <is>
-          <t>עוגת שוקולד</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E123" s="60" t="n">
@@ -11983,21 +11901,21 @@
       </c>
       <c r="B124" s="59" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C124" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D124" s="59" t="inlineStr">
         <is>
-          <t>עוגת שוקולד</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E124" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -12006,21 +11924,21 @@
       </c>
       <c r="B125" s="59" t="inlineStr">
         <is>
-          <t>שחר קרן</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C125" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D125" s="59" t="inlineStr">
         <is>
-          <t>עוגת שוקולד</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E125" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="126">
@@ -12029,21 +11947,21 @@
       </c>
       <c r="B126" s="59" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="C126" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D126" s="59" t="inlineStr">
         <is>
-          <t>עוגת שמרים</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E126" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="127">
@@ -12052,21 +11970,21 @@
       </c>
       <c r="B127" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C127" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D127" s="59" t="inlineStr">
         <is>
-          <t>עוגת שמרים</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E127" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
@@ -12075,21 +11993,21 @@
       </c>
       <c r="B128" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C128" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D128" s="59" t="inlineStr">
         <is>
-          <t>עוגת שמרים</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E128" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="129">
@@ -12098,21 +12016,21 @@
       </c>
       <c r="B129" s="59" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C129" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D129" s="59" t="inlineStr">
         <is>
-          <t>עוגת שמרים</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E129" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -12121,7 +12039,7 @@
       </c>
       <c r="B130" s="59" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C130" s="60" t="inlineStr">
@@ -12131,11 +12049,11 @@
       </c>
       <c r="D130" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E130" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="131">
@@ -12144,7 +12062,7 @@
       </c>
       <c r="B131" s="59" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C131" s="60" t="inlineStr">
@@ -12154,11 +12072,11 @@
       </c>
       <c r="D131" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E131" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="132">
@@ -12167,7 +12085,7 @@
       </c>
       <c r="B132" s="59" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף</t>
+          <t>שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="C132" s="60" t="inlineStr">
@@ -12177,11 +12095,11 @@
       </c>
       <c r="D132" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E132" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -12190,7 +12108,7 @@
       </c>
       <c r="B133" s="59" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C133" s="60" t="inlineStr">
@@ -12200,11 +12118,11 @@
       </c>
       <c r="D133" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E133" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="134">
@@ -12213,7 +12131,7 @@
       </c>
       <c r="B134" s="59" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C134" s="60" t="inlineStr">
@@ -12223,7 +12141,7 @@
       </c>
       <c r="D134" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E134" s="60" t="n">
@@ -12236,7 +12154,7 @@
       </c>
       <c r="B135" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C135" s="60" t="inlineStr">
@@ -12246,11 +12164,11 @@
       </c>
       <c r="D135" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E135" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -12269,11 +12187,11 @@
       </c>
       <c r="D136" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E136" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="137">
@@ -12282,7 +12200,7 @@
       </c>
       <c r="B137" s="59" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C137" s="60" t="inlineStr">
@@ -12292,11 +12210,11 @@
       </c>
       <c r="D137" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E137" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="138">
@@ -12305,7 +12223,7 @@
       </c>
       <c r="B138" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C138" s="60" t="inlineStr">
@@ -12315,11 +12233,11 @@
       </c>
       <c r="D138" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E138" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="139">
@@ -12328,7 +12246,7 @@
       </c>
       <c r="B139" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C139" s="60" t="inlineStr">
@@ -12338,11 +12256,11 @@
       </c>
       <c r="D139" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E139" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="140">
@@ -12351,7 +12269,7 @@
       </c>
       <c r="B140" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C140" s="60" t="inlineStr">
@@ -12361,11 +12279,11 @@
       </c>
       <c r="D140" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E140" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="141">
@@ -12374,7 +12292,7 @@
       </c>
       <c r="B141" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C141" s="60" t="inlineStr">
@@ -12384,11 +12302,11 @@
       </c>
       <c r="D141" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E141" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="142">
@@ -12397,7 +12315,7 @@
       </c>
       <c r="B142" s="59" t="inlineStr">
         <is>
-          <t>נבו בלוך</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C142" s="60" t="inlineStr">
@@ -12407,11 +12325,11 @@
       </c>
       <c r="D142" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E142" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="143">
@@ -12420,7 +12338,7 @@
       </c>
       <c r="B143" s="59" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>נדב טוקר</t>
         </is>
       </c>
       <c r="C143" s="60" t="inlineStr">
@@ -12430,11 +12348,11 @@
       </c>
       <c r="D143" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E143" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="144">
@@ -12443,7 +12361,7 @@
       </c>
       <c r="B144" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>רועי צבי סרי</t>
         </is>
       </c>
       <c r="C144" s="60" t="inlineStr">
@@ -12453,11 +12371,11 @@
       </c>
       <c r="D144" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E144" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="145">
@@ -12466,7 +12384,7 @@
       </c>
       <c r="B145" s="59" t="inlineStr">
         <is>
-          <t>תמר פרידמן</t>
+          <t>שחר קרן</t>
         </is>
       </c>
       <c r="C145" s="60" t="inlineStr">
@@ -12476,11 +12394,11 @@
       </c>
       <c r="D145" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E145" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="146">
@@ -12489,17 +12407,17 @@
       </c>
       <c r="B146" s="59" t="inlineStr">
         <is>
-          <t>תמר פרימור</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C146" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D146" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E146" s="60" t="n">
@@ -12512,21 +12430,21 @@
       </c>
       <c r="B147" s="59" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C147" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D147" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E147" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="148">
@@ -12535,21 +12453,21 @@
       </c>
       <c r="B148" s="59" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C148" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D148" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E148" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="149">
@@ -12558,21 +12476,21 @@
       </c>
       <c r="B149" s="59" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C149" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D149" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E149" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="150">
@@ -12581,21 +12499,21 @@
       </c>
       <c r="B150" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>בניה מעוז</t>
         </is>
       </c>
       <c r="C150" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D150" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E150" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="151">
@@ -12604,21 +12522,21 @@
       </c>
       <c r="B151" s="59" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C151" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D151" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E151" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="152">
@@ -12627,21 +12545,21 @@
       </c>
       <c r="B152" s="59" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C152" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D152" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E152" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="153">
@@ -12650,21 +12568,21 @@
       </c>
       <c r="B153" s="59" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C153" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D153" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E153" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="154">
@@ -12673,21 +12591,21 @@
       </c>
       <c r="B154" s="59" t="inlineStr">
         <is>
-          <t>רוני פרנקל</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C154" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D154" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E154" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155">
@@ -12696,21 +12614,21 @@
       </c>
       <c r="B155" s="59" t="inlineStr">
         <is>
-          <t>רועי צבי סרי</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C155" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D155" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E155" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="156">
@@ -12719,21 +12637,21 @@
       </c>
       <c r="B156" s="59" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C156" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D156" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E156" s="60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="157">
@@ -12742,21 +12660,21 @@
       </c>
       <c r="B157" s="59" t="inlineStr">
         <is>
-          <t>שילת פילפל</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C157" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D157" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E157" s="60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="158">
@@ -12765,21 +12683,21 @@
       </c>
       <c r="B158" s="59" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>נדב טוקר</t>
         </is>
       </c>
       <c r="C158" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D158" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E158" s="60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="159">
@@ -12788,7 +12706,7 @@
       </c>
       <c r="B159" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C159" s="60" t="inlineStr">
@@ -12798,7 +12716,7 @@
       </c>
       <c r="D159" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E159" s="60" t="n">
@@ -12811,7 +12729,7 @@
       </c>
       <c r="B160" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C160" s="60" t="inlineStr">
@@ -12821,7 +12739,7 @@
       </c>
       <c r="D160" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E160" s="60" t="n">
@@ -12834,7 +12752,7 @@
       </c>
       <c r="B161" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C161" s="60" t="inlineStr">
@@ -12844,7 +12762,7 @@
       </c>
       <c r="D161" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E161" s="60" t="n">
@@ -12857,7 +12775,7 @@
       </c>
       <c r="B162" s="59" t="inlineStr">
         <is>
-          <t>שחר קרן</t>
+          <t>רועי צבי סרי</t>
         </is>
       </c>
       <c r="C162" s="60" t="inlineStr">
@@ -12867,7 +12785,7 @@
       </c>
       <c r="D162" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת ערב</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E162" s="60" t="n">
@@ -12880,7 +12798,7 @@
       </c>
       <c r="B163" s="59" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="C163" s="60" t="inlineStr">
@@ -12890,7 +12808,7 @@
       </c>
       <c r="D163" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E163" s="60" t="n">
@@ -12903,7 +12821,7 @@
       </c>
       <c r="B164" s="59" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C164" s="60" t="inlineStr">
@@ -12913,7 +12831,7 @@
       </c>
       <c r="D164" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E164" s="60" t="n">
@@ -12926,7 +12844,7 @@
       </c>
       <c r="B165" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C165" s="60" t="inlineStr">
@@ -12936,7 +12854,7 @@
       </c>
       <c r="D165" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E165" s="60" t="n">
@@ -12949,7 +12867,7 @@
       </c>
       <c r="B166" s="59" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C166" s="60" t="inlineStr">
@@ -12959,7 +12877,7 @@
       </c>
       <c r="D166" s="59" t="inlineStr">
         <is>
-          <t>הכנת ארוחת צהריים שבת</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E166" s="60" t="n">
@@ -12972,7 +12890,7 @@
       </c>
       <c r="B167" s="59" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="C167" s="60" t="inlineStr">
@@ -12982,11 +12900,11 @@
       </c>
       <c r="D167" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E167" s="60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="168">
@@ -12995,7 +12913,7 @@
       </c>
       <c r="B168" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C168" s="60" t="inlineStr">
@@ -13005,11 +12923,11 @@
       </c>
       <c r="D168" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E168" s="60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="169">
@@ -13018,7 +12936,7 @@
       </c>
       <c r="B169" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C169" s="60" t="inlineStr">
@@ -13028,7 +12946,7 @@
       </c>
       <c r="D169" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E169" s="60" t="n">
@@ -13041,7 +12959,7 @@
       </c>
       <c r="B170" s="59" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C170" s="60" t="inlineStr">
@@ -13051,7 +12969,7 @@
       </c>
       <c r="D170" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E170" s="60" t="n">
@@ -13064,7 +12982,7 @@
       </c>
       <c r="B171" s="59" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="C171" s="60" t="inlineStr">
@@ -13074,7 +12992,7 @@
       </c>
       <c r="D171" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E171" s="60" t="n">
@@ -13087,21 +13005,21 @@
       </c>
       <c r="B172" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>אוריה תעשה</t>
         </is>
       </c>
       <c r="C172" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D172" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E172" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173">
@@ -13110,21 +13028,21 @@
       </c>
       <c r="B173" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C173" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D173" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E173" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="174">
@@ -13133,21 +13051,21 @@
       </c>
       <c r="B174" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C174" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D174" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E174" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="175">
@@ -13156,21 +13074,21 @@
       </c>
       <c r="B175" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C175" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D175" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E175" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="176">
@@ -13179,21 +13097,21 @@
       </c>
       <c r="B176" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>אנה עזריאל</t>
         </is>
       </c>
       <c r="C176" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D176" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E176" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="177">
@@ -13202,21 +13120,21 @@
       </c>
       <c r="B177" s="59" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>הילה לביא</t>
         </is>
       </c>
       <c r="C177" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D177" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E177" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="178">
@@ -13225,21 +13143,21 @@
       </c>
       <c r="B178" s="59" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C178" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D178" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E178" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -13248,21 +13166,21 @@
       </c>
       <c r="B179" s="59" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C179" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D179" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E179" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="180">
@@ -13271,21 +13189,21 @@
       </c>
       <c r="B180" s="59" t="inlineStr">
         <is>
-          <t>קובי סמייסון</t>
+          <t>רוני פרנקל</t>
         </is>
       </c>
       <c r="C180" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D180" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E180" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="181">
@@ -13294,21 +13212,21 @@
       </c>
       <c r="B181" s="59" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>תמר פרידמן</t>
         </is>
       </c>
       <c r="C181" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D181" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים שבת</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E181" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="182">
@@ -13317,21 +13235,21 @@
       </c>
       <c r="B182" s="59" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>תמר פרימור</t>
         </is>
       </c>
       <c r="C182" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D182" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E182" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="183">
@@ -13340,21 +13258,21 @@
       </c>
       <c r="B183" s="59" t="inlineStr">
         <is>
-          <t>בניה מעוז</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="C183" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D183" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E183" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="184">
@@ -13363,21 +13281,21 @@
       </c>
       <c r="B184" s="59" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C184" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D184" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E184" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="185">
@@ -13386,21 +13304,21 @@
       </c>
       <c r="B185" s="59" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>כליל בלאוקופף</t>
         </is>
       </c>
       <c r="C185" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D185" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E185" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="186">
@@ -13409,21 +13327,21 @@
       </c>
       <c r="B186" s="59" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="C186" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D186" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E186" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="187">
@@ -13432,7 +13350,7 @@
       </c>
       <c r="B187" s="59" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C187" s="60" t="inlineStr">
@@ -13442,7 +13360,7 @@
       </c>
       <c r="D187" s="59" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E187" s="60" t="n">
@@ -13455,7 +13373,7 @@
       </c>
       <c r="B188" s="59" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>עופר בביוף</t>
         </is>
       </c>
       <c r="C188" s="60" t="inlineStr">
@@ -13465,7 +13383,7 @@
       </c>
       <c r="D188" s="59" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E188" s="60" t="n">
@@ -13478,7 +13396,7 @@
       </c>
       <c r="B189" s="59" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>של״ו רובינשטיין</t>
         </is>
       </c>
       <c r="C189" s="60" t="inlineStr">
@@ -13488,378 +13406,10 @@
       </c>
       <c r="D189" s="59" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="E189" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B190" s="59" t="inlineStr">
-        <is>
-          <t>הילי אלפסי</t>
-        </is>
-      </c>
-      <c r="C190" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D190" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E190" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B191" s="59" t="inlineStr">
-        <is>
-          <t>כליל בלאוקופף</t>
-        </is>
-      </c>
-      <c r="C191" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D191" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E191" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B192" s="59" t="inlineStr">
-        <is>
-          <t>משה אוברשטיין</t>
-        </is>
-      </c>
-      <c r="C192" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D192" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E192" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B193" s="59" t="inlineStr">
-        <is>
-          <t>נועם ישראל קומפאס</t>
-        </is>
-      </c>
-      <c r="C193" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D193" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E193" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B194" s="59" t="inlineStr">
-        <is>
-          <t>רוני פרנקל</t>
-        </is>
-      </c>
-      <c r="C194" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D194" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E194" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B195" s="59" t="inlineStr">
-        <is>
-          <t>שחר מרקוביץ' גליק</t>
-        </is>
-      </c>
-      <c r="C195" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D195" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E195" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B196" s="59" t="inlineStr">
-        <is>
-          <t>שילת פילפל</t>
-        </is>
-      </c>
-      <c r="C196" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D196" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E196" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B197" s="59" t="inlineStr">
-        <is>
-          <t>של״ו רובינשטיין</t>
-        </is>
-      </c>
-      <c r="C197" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D197" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E197" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B198" s="59" t="inlineStr">
-        <is>
-          <t>תמר פרידמן</t>
-        </is>
-      </c>
-      <c r="C198" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D198" s="59" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E198" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B199" s="59" t="inlineStr">
-        <is>
-          <t>איתמר אסנהיים</t>
-        </is>
-      </c>
-      <c r="C199" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D199" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E199" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B200" s="59" t="inlineStr">
-        <is>
-          <t>איתן וינסטון</t>
-        </is>
-      </c>
-      <c r="C200" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D200" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E200" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B201" s="59" t="inlineStr">
-        <is>
-          <t>הילה עזרא</t>
-        </is>
-      </c>
-      <c r="C201" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D201" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E201" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B202" s="59" t="inlineStr">
-        <is>
-          <t>חיים שמאי</t>
-        </is>
-      </c>
-      <c r="C202" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D202" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E202" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B203" s="59" t="inlineStr">
-        <is>
-          <t>נגה שוהם</t>
-        </is>
-      </c>
-      <c r="C203" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D203" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E203" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B204" s="59" t="inlineStr">
-        <is>
-          <t>נדב טוקר</t>
-        </is>
-      </c>
-      <c r="C204" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D204" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E204" s="60" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" s="58" t="n">
-        <v>46311</v>
-      </c>
-      <c r="B205" s="59" t="inlineStr">
-        <is>
-          <t>שי- לי וולגמוט</t>
-        </is>
-      </c>
-      <c r="C205" s="60" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="D205" s="59" t="inlineStr">
-        <is>
-          <t>ניקיון חדר האוכל בשישי</t>
-        </is>
-      </c>
-      <c r="E205" s="60" t="n">
         <v>3</v>
       </c>
     </row>
@@ -14248,16 +13798,16 @@
       </c>
       <c r="C10" s="53" t="inlineStr">
         <is>
-          <t>4 ראשי כרוב (מלאה)</t>
+          <t>2 ראשי כרוב (לארוחה אחת)</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t>4 ראשי כרוב (קצוצים לרצועות דקות)
-מיץ מ-4–5 לימונים
-1.25 כוסות שמן זית (250–300 מ"ל)
-כ-2 כפות מלח (לפי הטעם)
-אופציונלי: כפית שטוחה סוכר / פלפל שחור / שמיר קצוץ</t>
+          <t>2 ראשי כרוב (קצוצים לרצועות דקות)
+מיץ מ-2–3 לימונים
+כ-⅔ כוס שמן זית (125–150 מ"ל)
+כ-1 כף מלח (לפי הטעם)
+אופציונלי: חצי כפית סוכר / פלפל שחור / שמיר קצוץ</t>
         </is>
       </c>
       <c r="E10" s="21" t="inlineStr">
@@ -14270,7 +13820,7 @@
       </c>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t>מכינים חצי כמות (2 כרובים) לכל ארוחה, סמוך להגשה</t>
+          <t>כמות לארוחה אחת — סמוך להגשה</t>
         </is>
       </c>
     </row>
@@ -14287,17 +13837,17 @@
       </c>
       <c r="C11" s="53" t="inlineStr">
         <is>
-          <t>3–4 חבילות טחינה (מלאה)</t>
+          <t>1.5–2 חבילות טחינה (לארוחה אחת)</t>
         </is>
       </c>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t>3–4 חבילות טחינה גולמית (או 2.5 אם הוספתם לחציל)
-מיץ מ-5–6 לימונים
-4–6 שיני שום כתושות
+          <t>1.5–2 חבילות טחינה גולמית
+מיץ מ-2.5–3 לימונים
+2–3 שיני שום כתושות
 מים קרים מאוד (בערך נפח הטחינה — להוסיף בהדרגה)
 מלח לפי הטעם
-2–3 כפות שמן זית לזילוף</t>
+1–2 כפות שמן זית לזילוף</t>
         </is>
       </c>
       <c r="E11" s="21" t="inlineStr">
@@ -14311,7 +13861,7 @@
       </c>
       <c r="F11" s="21" t="inlineStr">
         <is>
-          <t>מכינים חצי כמות לכל ארוחה, סמוך להגשה</t>
+          <t>כמות לארוחה אחת — סמוך להגשה</t>
         </is>
       </c>
     </row>
@@ -15040,7 +14590,7 @@
     <row r="84" ht="28" customHeight="1">
       <c r="A84" s="26" t="inlineStr">
         <is>
-          <t>שם המנה (עמודה B) הוא מה שבוחרים בעמודת «מתכון» ב«משימות» — והמצרכים מודפסים על הפלייר של הקבוצה (ההוראות רק עם --with-recipes). מרכיבים והוראות: שורה לכל פריט (Alt+Enter לשורה חדשה בתא).</t>
+          <t>שם המנה (עמודה B) הוא מה שבוחרים בעמודת «מתכון» ב«משימות» — והמצרכים מודפסים על הפלייר של הקבוצה (גם המצרכים וגם אופן ההכנה, בדף של התורנות). מרכיבים והוראות: שורה לכל פריט (Alt+Enter לשורה חדשה בתא).</t>
         </is>
       </c>
     </row>
@@ -15357,14 +14907,30 @@
       <c r="D20" s="21" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="53" t="n"/>
-      <c r="B21" s="48" t="n"/>
+      <c r="A21" s="53" t="inlineStr">
+        <is>
+          <t>מההכנות לערב</t>
+        </is>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>חצי מהמטבוחה, חצי מסלט החצילים וחצי מהחלות</t>
+        </is>
+      </c>
       <c r="C21" s="53" t="n"/>
       <c r="D21" s="21" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="53" t="n"/>
-      <c r="B22" s="48" t="n"/>
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>מההכנות לצהריים</t>
+        </is>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>שאר המטבוחה, סלט החצילים והחלות</t>
+        </is>
+      </c>
       <c r="C22" s="53" t="n"/>
       <c r="D22" s="21" t="n"/>
     </row>

--- a/shabbatot/2026-10-16.xlsx
+++ b/shabbatot/2026-10-16.xlsx
@@ -1507,7 +1507,7 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>דבר תורה ושירה</t>
+          <t>דבר תורה ושירה · מעבירים: איתן כהן</t>
         </is>
       </c>
       <c r="F18" s="49" t="n">
@@ -1933,11 +1933,11 @@
         </is>
       </c>
       <c r="F3" s="53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G3" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד</t>
+          <t>רוני כהן, ניצן גמלא, הלל פינגולד</t>
         </is>
       </c>
       <c r="H3" s="48" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="E5" s="21" t="inlineStr">
         <is>
-          <t>עוגת שוקולד — 6 עוגות אינגליש קייק</t>
+          <t>עוגת שוקולד — 12 עוגות אינגליש קייק</t>
         </is>
       </c>
       <c r="F5" s="53" t="n">
@@ -2031,7 +2031,7 @@
       </c>
       <c r="G5" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, רוני כהן</t>
+          <t>הילה לביא, בניה מעוז</t>
         </is>
       </c>
       <c r="H5" s="48" t="inlineStr">
@@ -2080,7 +2080,7 @@
       </c>
       <c r="G6" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, הדר עמדי, זואי כהן</t>
+          <t>איתן כהן, רגב שהם, אלרואי גרינברג</t>
         </is>
       </c>
       <c r="H6" s="48" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="G7" s="31" t="inlineStr">
         <is>
-          <t>עמית סיילס, שחר קרן, עמית שי אברהם, שירה ספונוב</t>
+          <t>ליבי בוכריס, הדר עמדי, שחר קרן, אלה גוטליב</t>
         </is>
       </c>
       <c r="H7" s="48" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="G9" s="31" t="inlineStr">
         <is>
-          <t>אחיה נחמני, אלה גוטליב</t>
+          <t>מאיה פקטר, קובי סמייסון</t>
         </is>
       </c>
       <c r="H9" s="48" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G10" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, קובי סמייסון, יערה ריס, נבו בלוך</t>
+          <t>של״ו רובינשטיין, עמית סיילס, עמית שי אברהם, אחיה נחמני</t>
         </is>
       </c>
       <c r="H10" s="48" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="G11" s="31" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס, של״ו רובינשטיין, יהב לוי, נגה חוה כהן, ירדן בן שחר, כליל בלאוקופף, עופר בביוף</t>
+          <t>איתי בן מנחם, נועם ישראל קומפאס, ירדן בן שחר, אנה עזריאל, משה אוברשטיין, נגה חוה כהן, תמר פרימור</t>
         </is>
       </c>
       <c r="H11" s="48" t="n"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G12" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, ירדן בן שחר, רותם דרור, תמר פרידמן, איתן כהן</t>
+          <t>אלה גוטליב, שחר קרן, ירדן בן שחר, משה אוברשטיין, תמר פרידמן</t>
         </is>
       </c>
       <c r="H12" s="48" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, קובי סמייסון</t>
+          <t>של״ו רובינשטיין, עמית סיילס</t>
         </is>
       </c>
       <c r="H13" s="48" t="n"/>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>יערה ריס, נבו בלוך</t>
+          <t>עמית שי אברהם, אחיה נחמני</t>
         </is>
       </c>
       <c r="H14" s="48" t="n"/>
@@ -2484,11 +2484,11 @@
         </is>
       </c>
       <c r="F15" s="53" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן, אלה מאיר, אנה עזריאל, איתי בן מנחם, רוני פרנקל, תמר פרימור, יובל יצחק, איתן כהן</t>
+          <t>יהב לוי, זואי כהן, שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן, הילי אלפסי, כליל בלאוקופף, רוני פרנקל, נבו בלוך, טליה קור</t>
         </is>
       </c>
       <c r="H15" s="48" t="n"/>
@@ -2524,11 +2524,11 @@
         </is>
       </c>
       <c r="F16" s="53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן</t>
+          <t>שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן</t>
         </is>
       </c>
       <c r="H16" s="48" t="n"/>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, אנה עזריאל</t>
+          <t>יהב לוי, הילי אלפסי</t>
         </is>
       </c>
       <c r="H17" s="48" t="n"/>
@@ -2608,7 +2608,7 @@
       </c>
       <c r="G18" s="31" t="inlineStr">
         <is>
-          <t>איתי בן מנחם, רוני פרנקל, תמר פרימור</t>
+          <t>כליל בלאוקופף, רוני פרנקל, נבו בלוך</t>
         </is>
       </c>
       <c r="H18" s="48" t="n"/>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>יובל יצחק, איתן כהן</t>
+          <t>זואי כהן, טליה קור</t>
         </is>
       </c>
       <c r="H19" s="48" t="n"/>
@@ -2688,7 +2688,7 @@
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H20" s="48" t="n"/>
@@ -2729,7 +2729,7 @@
       </c>
       <c r="G21" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H21" s="48" t="n"/>
@@ -2769,7 +2769,7 @@
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H22" s="48" t="n"/>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="G23" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H23" s="48" t="n"/>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="G24" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H24" s="48" t="n"/>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="G25" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, מעיין יוספי, ניתאי שלום</t>
+          <t>מעיין רחל דינר, יונתן לירז, מעיין יוספי</t>
         </is>
       </c>
       <c r="H25" s="48" t="inlineStr">
@@ -2927,7 +2927,7 @@
         <is>
           <t>עריכת השולחן:
 סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס
-חצי מהמטבוחה, חצי מסלט החצילים וחצי מהחלות
+חצי מהמטבוחה, חצי סלט חצילים וחצי חלות
 צלחות וסכו"ם</t>
         </is>
       </c>
@@ -2936,7 +2936,7 @@
       </c>
       <c r="G26" s="31" t="inlineStr">
         <is>
-          <t>ינון לוי, יונתן לירז, מעיין יוספי, ניתאי שלום</t>
+          <t>ניתאי שלום, מעיין רחל דינר, יונתן לירז, מעיין יוספי</t>
         </is>
       </c>
       <c r="H26" s="48" t="n"/>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G27" s="31" t="inlineStr">
         <is>
-          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
+          <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
         </is>
       </c>
       <c r="H27" s="48" t="n"/>
@@ -3017,7 +3017,7 @@
       <c r="F28" s="53" t="n"/>
       <c r="G28" s="31" t="inlineStr">
         <is>
-          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
+          <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
         </is>
       </c>
       <c r="H28" s="48" t="n"/>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E29" s="21" t="inlineStr">
         <is>
-          <t>חימום העוגות — הכל פרווה
+          <t>חימום 3 פסי עוגת שוקולד, 3 פסי עוגת שמרים — הכל פרווה
 חיתוך 10 תפוחים
 סידור המרחב: שולחנות בקוביה במרכז, כיסאות במעגל מסביב
 פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
@@ -3060,7 +3060,7 @@
       </c>
       <c r="G29" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
+          <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
         </is>
       </c>
       <c r="H29" s="48" t="n"/>
@@ -3096,7 +3096,7 @@
       <c r="F30" s="53" t="n"/>
       <c r="G30" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
+          <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
         </is>
       </c>
       <c r="H30" s="48" t="n"/>
@@ -3130,7 +3130,7 @@
         <is>
           <t>סידור וניקיון פינת הקפה — להוציא חלב, למלא קפה וסוכר
 חימום העוגות
-הוצאת העוגות
+הוצאת 5 פסי עוגת שוקולד, 5 פסי עוגת שמרים
 הוצאת חלב, קורנפלקס וחצי מהענבים
 טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
@@ -3140,7 +3140,7 @@
       </c>
       <c r="G31" s="31" t="inlineStr">
         <is>
-          <t>ניצן גמלא, הלל פינגולד, אלרואי גרינברג</t>
+          <t>ניצן גמלא, הלל פינגולד, ליבי בוכריס</t>
         </is>
       </c>
       <c r="H31" s="48" t="n"/>
@@ -3174,7 +3174,7 @@
         <is>
           <t>עריכת השולחן:
 הכנת סלט כרוב מרענן, סלט טחינה ביתית
-הוצאת שאר המטבוחה, סלט החצילים והחלות
+הוצאת חצי מהמטבוחה, חצי סלט חצילים וחצי חלות
 סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס</t>
         </is>
       </c>
@@ -3183,7 +3183,7 @@
       </c>
       <c r="G32" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, רגב שהם</t>
+          <t>אלרואי גרינברג, בניה מעוז</t>
         </is>
       </c>
       <c r="H32" s="48" t="inlineStr">
@@ -3228,7 +3228,7 @@
       </c>
       <c r="G33" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, הדר עמדי</t>
+          <t>רגב שהם, רוני כהן</t>
         </is>
       </c>
       <c r="H33" s="48" t="n"/>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G34" s="31" t="inlineStr">
         <is>
-          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
+          <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
         </is>
       </c>
       <c r="H34" s="48" t="n"/>
@@ -3309,7 +3309,7 @@
       <c r="F35" s="53" t="n"/>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
+          <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
         </is>
       </c>
       <c r="H35" s="48" t="n"/>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>הוצאת העוגות לסעודה שלישית</t>
+          <t>הוצאת ג'חנון, רסק עגבניות וביצים (מהקייטרינג), 4 פסי עוגת שוקולד, 4 פסי עוגת שמרים לסעודה שלישית</t>
         </is>
       </c>
       <c r="F36" s="53" t="n">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>רוני כהן, עמית שי אברהם</t>
+          <t>הדר עמדי, נגה שוהם</t>
         </is>
       </c>
       <c r="H36" s="48" t="n"/>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="G37" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, מעיין יוספי, יונתן לירז, משה אוברשטיין, אביה וייל, יערה ריס, שחר מרקוביץ' גליק, עמית סיילס, מאיה פקטר, שילת פילפל</t>
+          <t>מעיין רחל דינר, ניתאי שלום, מעיין יוספי, ארבל פרנקו, אוריה תעשה, יונתן לירז, אביה וייל, שירה ספונוב, יערה ריס, חיים שמאי</t>
         </is>
       </c>
       <c r="H37" s="48" t="n"/>
@@ -3430,7 +3430,7 @@
       </c>
       <c r="G38" s="31" t="inlineStr">
         <is>
-          <t>רועי צבי סרי, נגה שוהם, ינון לוי, נדב טוקר, הילי אלפסי, אחיה נחמני, ארבל פרנקו, חיים שמאי, אלה גוטליב, זואי כהן, יואב אוחנה, שחר קרן</t>
+          <t>איתמר אסנהיים, מאיה פקטר, יובל יצחק, שילת פילפל, איתן וינסטון, רועי צבי סרי, ינון לוי, עמית סיילס, יואב אוחנה, נדב טוקר, אלה מאיר, עמית שי אברהם</t>
         </is>
       </c>
       <c r="H38" s="48" t="n"/>
@@ -4563,12 +4563,12 @@
       </c>
       <c r="D3" s="34" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="E3" s="31" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג, ניצן גמלא, רגב שהם, הלל פינגולד</t>
+          <t>רוני כהן, ניצן גמלא, הלל פינגולד</t>
         </is>
       </c>
       <c r="F3" s="50">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="D4" s="34" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="E4" s="31" t="n"/>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="D5" s="34" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>הילה לביא</t>
         </is>
       </c>
       <c r="E5" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, רוני כהן</t>
+          <t>הילה לביא, בניה מעוז</t>
         </is>
       </c>
       <c r="F5" s="50">
@@ -4658,12 +4658,12 @@
       </c>
       <c r="D6" s="34" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="E6" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, הדר עמדי, זואי כהן</t>
+          <t>איתן כהן, רגב שהם, אלרואי גרינברג</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -4691,12 +4691,12 @@
       </c>
       <c r="D7" s="34" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="E7" s="31" t="inlineStr">
         <is>
-          <t>עמית סיילס, שחר קרן, עמית שי אברהם, שירה ספונוב</t>
+          <t>ליבי בוכריס, הדר עמדי, שחר קרן, אלה גוטליב</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -4724,7 +4724,7 @@
       </c>
       <c r="D8" s="34" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="E8" s="31" t="n"/>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="D9" s="34" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="E9" s="31" t="inlineStr">
         <is>
-          <t>אחיה נחמני, אלה גוטליב</t>
+          <t>מאיה פקטר, קובי סמייסון</t>
         </is>
       </c>
       <c r="F9" s="50">
@@ -4786,12 +4786,12 @@
       </c>
       <c r="D10" s="34" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>של״ו רובינשטיין</t>
         </is>
       </c>
       <c r="E10" s="31" t="inlineStr">
         <is>
-          <t>מאיה פקטר, קובי סמייסון, יערה ריס, נבו בלוך</t>
+          <t>של״ו רובינשטיין, עמית סיילס, עמית שי אברהם, אחיה נחמני</t>
         </is>
       </c>
       <c r="F10" s="50">
@@ -4819,12 +4819,12 @@
       </c>
       <c r="D11" s="34" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="E11" s="31" t="inlineStr">
         <is>
-          <t>הילה לביא, טליה קור, אוריה תעשה, תמר פרידמן, אלה מאיר, אנה עזריאל, איתי בן מנחם, רוני פרנקל, תמר פרימור, יובל יצחק, איתן כהן</t>
+          <t>יהב לוי, זואי כהן, שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן, הילי אלפסי, כליל בלאוקופף, רוני פרנקל, נבו בלוך, טליה קור</t>
         </is>
       </c>
       <c r="F11" s="50">
@@ -4852,12 +4852,12 @@
       </c>
       <c r="D12" s="34" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="E12" s="31" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס, של״ו רובינשטיין, יהב לוי, נגה חוה כהן, ירדן בן שחר, כליל בלאוקופף, עופר בביוף</t>
+          <t>איתי בן מנחם, נועם ישראל קומפאס, ירדן בן שחר, אנה עזריאל, משה אוברשטיין, נגה חוה כהן, תמר פרימור</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="D13" s="34" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="E13" s="31" t="inlineStr">
         <is>
-          <t>שילת פילפל, הילי אלפסי</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="F13" s="50">
@@ -4923,7 +4923,7 @@
       </c>
       <c r="E14" s="31" t="inlineStr">
         <is>
-          <t>יונתן לירז, מעיין יוספי, ניתאי שלום, ינון לוי</t>
+          <t>מעיין רחל דינר, יונתן לירז, מעיין יוספי, ניתאי שלום</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -4956,7 +4956,7 @@
       </c>
       <c r="E15" s="31" t="inlineStr">
         <is>
-          <t>אביה וייל, יואב אוחנה, רועי צבי סרי, ארבל פרנקו, שחר מרקוביץ' גליק</t>
+          <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -4984,12 +4984,12 @@
       </c>
       <c r="D16" s="34" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>נדב טוקר</t>
         </is>
       </c>
       <c r="E16" s="31" t="inlineStr">
         <is>
-          <t>משה אוברשטיין, נדב טוקר, נגה שוהם</t>
+          <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
         </is>
       </c>
       <c r="F16" s="50">
@@ -5017,12 +5017,12 @@
       </c>
       <c r="D17" s="34" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
         <is>
-          <t>ניצן גמלא, הלל פינגולד, אלרואי גרינברג</t>
+          <t>ניצן גמלא, הלל פינגולד, ליבי בוכריס</t>
         </is>
       </c>
       <c r="F17" s="50">
@@ -5050,12 +5050,12 @@
       </c>
       <c r="D18" s="34" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="E18" s="31" t="inlineStr">
         <is>
-          <t>בניה מעוז, רגב שהם, מעיין רחל דינר, הדר עמדי</t>
+          <t>אלרואי גרינברג, בניה מעוז, רגב שהם, רוני כהן</t>
         </is>
       </c>
       <c r="F18" s="50">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="D19" s="34" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="E19" s="31" t="inlineStr">
         <is>
-          <t>רוני כהן, עמית שי אברהם, קובי סמייסון, איתמר אסנהיים, איתן וינסטון</t>
+          <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="D20" s="34" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="E20" s="31" t="inlineStr">
         <is>
-          <t>ניתאי שלום, מעיין יוספי, יונתן לירז, משה אוברשטיין, אביה וייל, יערה ריס, שחר מרקוביץ' גליק, עמית סיילס, מאיה פקטר, שילת פילפל</t>
+          <t>מעיין רחל דינר, ניתאי שלום, מעיין יוספי, ארבל פרנקו, אוריה תעשה, יונתן לירז, אביה וייל, שירה ספונוב, יערה ריס, חיים שמאי</t>
         </is>
       </c>
       <c r="F20" s="50">
@@ -5149,12 +5149,12 @@
       </c>
       <c r="D21" s="34" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="E21" s="31" t="inlineStr">
         <is>
-          <t>רועי צבי סרי, נגה שוהם, ינון לוי, נדב טוקר, הילי אלפסי, אחיה נחמני, ארבל פרנקו, חיים שמאי, אלה גוטליב, זואי כהן, יואב אוחנה, שחר קרן</t>
+          <t>איתמר אסנהיים, מאיה פקטר, יובל יצחק, שילת פילפל, איתן וינסטון, רועי צבי סרי, ינון לוי, עמית סיילס, יואב אוחנה, נדב טוקר, אלה מאיר, עמית שי אברהם</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -5182,12 +5182,12 @@
       </c>
       <c r="D22" s="34" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="E22" s="31" t="inlineStr">
         <is>
-          <t>שירה ספונוב, ירדן בן שחר, רותם דרור, תמר פרידמן, איתן כהן</t>
+          <t>אלה גוטליב, שחר קרן, ירדן בן שחר, משה אוברשטיין, תמר פרידמן</t>
         </is>
       </c>
       <c r="F22" s="50">
@@ -5508,7 +5508,7 @@
       </c>
       <c r="E4" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F4" s="50">
@@ -5516,7 +5516,7 @@
         <v/>
       </c>
       <c r="G4" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H4" s="50">
         <f>IF(A4="","",SUMIF('היסטוריה'!$B$3:$B$3002,A4,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5547,7 +5547,7 @@
       </c>
       <c r="E5" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F5" s="50">
@@ -5555,7 +5555,7 @@
         <v/>
       </c>
       <c r="G5" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H5" s="50">
         <f>IF(A5="","",SUMIF('היסטוריה'!$B$3:$B$3002,A5,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5586,7 +5586,7 @@
       </c>
       <c r="E6" s="34" t="inlineStr">
         <is>
-          <t>גסטרונומים; ניקיון חדר האוכל במוצ"ש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F6" s="50">
@@ -5594,7 +5594,7 @@
         <v/>
       </c>
       <c r="G6" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H6" s="50">
         <f>IF(A6="","",SUMIF('היסטוריה'!$B$3:$B$3002,A6,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="E7" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F7" s="50">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="E8" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ניקיון חדר האוכל במוצ"ש</t>
+          <t>מטבוחה; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F8" s="50">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="E10" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל במוצ"ש</t>
+          <t>ארוחת צהריים שישי; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F10" s="50">
@@ -5750,7 +5750,7 @@
         <v/>
       </c>
       <c r="G10" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" s="50">
         <f>IF(A10="","",SUMIF('היסטוריה'!$B$3:$B$3002,A10,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5820,7 +5820,7 @@
       </c>
       <c r="E12" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ניקיון בית המדרש במוצ"ש</t>
+          <t>ארוחת צהריים שישי; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F12" s="50">
@@ -5828,7 +5828,7 @@
         <v/>
       </c>
       <c r="G12" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H12" s="50">
         <f>IF(A12="","",SUMIF('היסטוריה'!$B$3:$B$3002,A12,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5888,7 +5888,7 @@
       </c>
       <c r="E14" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון בית המדרש במוצ"ש</t>
+          <t>ניקיון חדר האוכל בשישי; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F14" s="50">
@@ -5896,7 +5896,7 @@
         <v/>
       </c>
       <c r="G14" s="35" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H14" s="50">
         <f>IF(A14="","",SUMIF('היסטוריה'!$B$3:$B$3002,A14,'היסטוריה'!$E$3:$E$3002))</f>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="E15" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>טיש; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F15" s="50">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="E19" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; ארוחת צהריים שבת</t>
+          <t>מטבוחה; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F19" s="50">
@@ -6151,7 +6151,7 @@
       </c>
       <c r="E21" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F21" s="50">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="E24" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F24" s="50">
@@ -6262,7 +6262,7 @@
         <v/>
       </c>
       <c r="G24" s="35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H24" s="50">
         <f>IF(A24="","",SUMIF('היסטוריה'!$B$3:$B$3002,A24,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="E25" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל במוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F25" s="50">
@@ -6301,7 +6301,7 @@
         <v/>
       </c>
       <c r="G25" s="35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H25" s="50">
         <f>IF(A25="","",SUMIF('היסטוריה'!$B$3:$B$3002,A25,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="E26" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F26" s="50">
@@ -6371,7 +6371,7 @@
       </c>
       <c r="E27" s="34" t="inlineStr">
         <is>
-          <t>חלות; קידוש</t>
+          <t>עוגת שמרים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F27" s="50">
@@ -6379,7 +6379,7 @@
         <v/>
       </c>
       <c r="G27" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H27" s="50">
         <f>IF(A27="","",SUMIF('היסטוריה'!$B$3:$B$3002,A27,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="E28" s="34" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל במוצ"ש</t>
+          <t>מטבוחה; ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="F28" s="50">
@@ -6447,18 +6447,12 @@
           <t>כן</t>
         </is>
       </c>
-      <c r="E29" s="34" t="inlineStr">
-        <is>
-          <t>ארוחת ערב מוצ"ש</t>
-        </is>
-      </c>
+      <c r="E29" s="34" t="n"/>
       <c r="F29" s="50">
         <f>IF(A29="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A29&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G29" s="35" t="n">
-        <v>3</v>
-      </c>
+      <c r="G29" s="35" t="n"/>
       <c r="H29" s="50">
         <f>IF(A29="","",SUMIF('היסטוריה'!$B$3:$B$3002,A29,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
@@ -6546,7 +6540,7 @@
       </c>
       <c r="E32" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; ארוחת ערב מוצ"ש</t>
+          <t>בית מדרש; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F32" s="50">
@@ -6554,7 +6548,7 @@
         <v/>
       </c>
       <c r="G32" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H32" s="50">
         <f>IF(A32="","",SUMIF('היסטוריה'!$B$3:$B$3002,A32,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6624,7 +6618,7 @@
       </c>
       <c r="E34" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; ארוחת צהריים שבת</t>
+          <t>ארוחת ערב; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F34" s="50">
@@ -6632,7 +6626,7 @@
         <v/>
       </c>
       <c r="G34" s="35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H34" s="50">
         <f>IF(A34="","",SUMIF('היסטוריה'!$B$3:$B$3002,A34,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6727,7 +6721,7 @@
       </c>
       <c r="E37" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>עוגיות שוקולד צ'יפס; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F37" s="50">
@@ -6766,7 +6760,7 @@
       </c>
       <c r="E38" s="34" t="inlineStr">
         <is>
-          <t>טיש; ניקיון חדר האוכל במוצ"ש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F38" s="50">
@@ -6774,7 +6768,7 @@
         <v/>
       </c>
       <c r="G38" s="35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H38" s="50">
         <f>IF(A38="","",SUMIF('היסטוריה'!$B$3:$B$3002,A38,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6805,7 +6799,7 @@
       </c>
       <c r="E39" s="34" t="inlineStr">
         <is>
-          <t>ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
+          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F39" s="50">
@@ -6844,7 +6838,7 @@
       </c>
       <c r="E40" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>גסטרונומים; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F40" s="50">
@@ -6852,7 +6846,7 @@
         <v/>
       </c>
       <c r="G40" s="35" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H40" s="50">
         <f>IF(A40="","",SUMIF('היסטוריה'!$B$3:$B$3002,A40,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6883,7 +6877,7 @@
       </c>
       <c r="E41" s="34" t="inlineStr">
         <is>
-          <t>עוגת שמרים; ניקיון חדר האוכל במוצ"ש</t>
+          <t>בית מדרש; פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="F41" s="50">
@@ -6891,7 +6885,7 @@
         <v/>
       </c>
       <c r="G41" s="35" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H41" s="50">
         <f>IF(A41="","",SUMIF('היסטוריה'!$B$3:$B$3002,A41,'היסטוריה'!$E$3:$E$3002))</f>
@@ -6922,7 +6916,7 @@
       </c>
       <c r="E42" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>ארוחת צהריים שישי</t>
         </is>
       </c>
       <c r="F42" s="50">
@@ -6961,7 +6955,7 @@
       </c>
       <c r="E43" s="34" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל בשישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F43" s="50">
@@ -7068,7 +7062,7 @@
       </c>
       <c r="E46" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>עוגת שוקולד</t>
         </is>
       </c>
       <c r="F46" s="50">
@@ -7107,7 +7101,7 @@
       </c>
       <c r="E47" s="34" t="inlineStr">
         <is>
-          <t>מטבוחה; פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>ארוחת צהריים שישי; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F47" s="50">
@@ -7115,7 +7109,7 @@
         <v/>
       </c>
       <c r="G47" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H47" s="50">
         <f>IF(A47="","",SUMIF('היסטוריה'!$B$3:$B$3002,A47,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7146,7 +7140,7 @@
       </c>
       <c r="E48" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F48" s="50">
@@ -7185,7 +7179,7 @@
       </c>
       <c r="E49" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="F49" s="50">
@@ -7224,7 +7218,7 @@
       </c>
       <c r="E50" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב; ניקיון חדר האוכל במוצ"ש</t>
+          <t>טיש; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F50" s="50">
@@ -7232,7 +7226,7 @@
         <v/>
       </c>
       <c r="G50" s="35" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H50" s="50">
         <f>IF(A50="","",SUMIF('היסטוריה'!$B$3:$B$3002,A50,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7360,7 +7354,7 @@
       </c>
       <c r="E54" s="34" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F54" s="50">
@@ -7368,7 +7362,7 @@
         <v/>
       </c>
       <c r="G54" s="35" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H54" s="50">
         <f>IF(A54="","",SUMIF('היסטוריה'!$B$3:$B$3002,A54,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7432,7 +7426,7 @@
       </c>
       <c r="E56" s="34" t="inlineStr">
         <is>
-          <t>גסטרונומים; ניקיון בית המדרש במוצ"ש</t>
+          <t>גסטרונומים; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F56" s="50">
@@ -7440,7 +7434,7 @@
         <v/>
       </c>
       <c r="G56" s="35" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H56" s="50">
         <f>IF(A56="","",SUMIF('היסטוריה'!$B$3:$B$3002,A56,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7549,7 +7543,7 @@
       </c>
       <c r="E59" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש; ארוחת ערב מוצ"ש</t>
+          <t>עוגת שמרים</t>
         </is>
       </c>
       <c r="F59" s="50">
@@ -7557,7 +7551,7 @@
         <v/>
       </c>
       <c r="G59" s="35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H59" s="50">
         <f>IF(A59="","",SUMIF('היסטוריה'!$B$3:$B$3002,A59,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7588,7 +7582,7 @@
       </c>
       <c r="E60" s="34" t="inlineStr">
         <is>
-          <t>בית מדרש</t>
+          <t>ניקיון חדר האוכל בשישי</t>
         </is>
       </c>
       <c r="F60" s="50">
@@ -7773,7 +7767,7 @@
       </c>
       <c r="E65" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון בית המדרש במוצ"ש</t>
+          <t>בית מדרש; ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="F65" s="50">
@@ -7830,22 +7824,28 @@
         </is>
       </c>
       <c r="C67" s="35" t="n"/>
-      <c r="D67" s="35" t="n"/>
-      <c r="E67" s="34" t="n"/>
+      <c r="D67" s="35" t="inlineStr">
+        <is>
+          <t>כן</t>
+        </is>
+      </c>
+      <c r="E67" s="34" t="inlineStr">
+        <is>
+          <t>מטבוחה; קידוש</t>
+        </is>
+      </c>
       <c r="F67" s="50">
         <f>IF(A67="","",COUNTIF('משימות'!$G$3:$G$122,"*"&amp;A67&amp;"*"))</f>
         <v/>
       </c>
-      <c r="G67" s="35" t="n"/>
+      <c r="G67" s="35" t="n">
+        <v>4</v>
+      </c>
       <c r="H67" s="50">
         <f>IF(A67="","",SUMIF('היסטוריה'!$B$3:$B$3002,A67,'היסטוריה'!$E$3:$E$3002))</f>
         <v/>
       </c>
-      <c r="I67" s="34" t="inlineStr">
-        <is>
-          <t>לא נוכח/ת</t>
-        </is>
-      </c>
+      <c r="I67" s="34" t="n"/>
     </row>
     <row r="68">
       <c r="A68" s="48" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="E69" s="34" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי; ניקיון בית המדרש במוצ"ש</t>
+          <t>עוגיות שוקולד צ'יפס; ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="F69" s="50">
@@ -7907,7 +7907,7 @@
         <v/>
       </c>
       <c r="G69" s="35" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H69" s="50">
         <f>IF(A69="","",SUMIF('היסטוריה'!$B$3:$B$3002,A69,'היסטוריה'!$E$3:$E$3002))</f>
@@ -7963,7 +7963,7 @@
       </c>
       <c r="E71" s="34" t="inlineStr">
         <is>
-          <t>חלות; ארוחת צהריים שבת</t>
+          <t>עוגת שמרים; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F71" s="50">
@@ -8002,7 +8002,7 @@
       </c>
       <c r="E72" s="34" t="inlineStr">
         <is>
-          <t>עוגת שוקולד; פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>חלות; ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="F72" s="50">
@@ -11349,7 +11349,7 @@
       </c>
       <c r="B100" s="59" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C100" s="60" t="inlineStr">
@@ -11372,7 +11372,7 @@
       </c>
       <c r="B101" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C101" s="60" t="inlineStr">
@@ -11395,7 +11395,7 @@
       </c>
       <c r="B102" s="59" t="inlineStr">
         <is>
-          <t>נבו בלוך</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C102" s="60" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="B103" s="59" t="inlineStr">
         <is>
-          <t>קובי סמייסון</t>
+          <t>של״ו רובינשטיין</t>
         </is>
       </c>
       <c r="C103" s="60" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="B104" s="59" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C104" s="60" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="B105" s="59" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="C105" s="60" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="B106" s="59" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C106" s="60" t="inlineStr">
@@ -11510,7 +11510,7 @@
       </c>
       <c r="B107" s="59" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C107" s="60" t="inlineStr">
@@ -11520,7 +11520,7 @@
       </c>
       <c r="D107" s="59" t="inlineStr">
         <is>
-          <t>חלות</t>
+          <t>מטבוחה</t>
         </is>
       </c>
       <c r="E107" s="60" t="n">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="B108" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C108" s="60" t="inlineStr">
@@ -11556,7 +11556,7 @@
       </c>
       <c r="B109" s="59" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="C109" s="60" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="B111" s="59" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C111" s="60" t="inlineStr">
@@ -11612,7 +11612,7 @@
       </c>
       <c r="D111" s="59" t="inlineStr">
         <is>
-          <t>מטבוחה</t>
+          <t>עוגיות שוקולד צ'יפס</t>
         </is>
       </c>
       <c r="E111" s="60" t="n">
@@ -11625,7 +11625,7 @@
       </c>
       <c r="B112" s="59" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>קובי סמייסון</t>
         </is>
       </c>
       <c r="C112" s="60" t="inlineStr">
@@ -11648,7 +11648,7 @@
       </c>
       <c r="B113" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>בניה מעוז</t>
         </is>
       </c>
       <c r="C113" s="60" t="inlineStr">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="D113" s="59" t="inlineStr">
         <is>
-          <t>עוגיות שוקולד צ'יפס</t>
+          <t>עוגת שוקולד</t>
         </is>
       </c>
       <c r="E113" s="60" t="n">
@@ -11671,7 +11671,7 @@
       </c>
       <c r="B114" s="59" t="inlineStr">
         <is>
-          <t>בניה מעוז</t>
+          <t>הילה לביא</t>
         </is>
       </c>
       <c r="C114" s="60" t="inlineStr">
@@ -11694,7 +11694,7 @@
       </c>
       <c r="B115" s="59" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>איתן כהן</t>
         </is>
       </c>
       <c r="C115" s="60" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="D115" s="59" t="inlineStr">
         <is>
-          <t>עוגת שוקולד</t>
+          <t>עוגת שמרים</t>
         </is>
       </c>
       <c r="E115" s="60" t="n">
@@ -11717,7 +11717,7 @@
       </c>
       <c r="B116" s="59" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C116" s="60" t="inlineStr">
@@ -11740,7 +11740,7 @@
       </c>
       <c r="B117" s="59" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C117" s="60" t="inlineStr">
@@ -11763,17 +11763,17 @@
       </c>
       <c r="B118" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>אלה גוטליב</t>
         </is>
       </c>
       <c r="C118" s="60" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
+          <t>תורנות מוצ"ש</t>
         </is>
       </c>
       <c r="D118" s="59" t="inlineStr">
         <is>
-          <t>עוגת שמרים</t>
+          <t>ארוחת ערב מוצ"ש</t>
         </is>
       </c>
       <c r="E118" s="60" t="n">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="B119" s="59" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C119" s="60" t="inlineStr">
@@ -11809,7 +11809,7 @@
       </c>
       <c r="B120" s="59" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C120" s="60" t="inlineStr">
@@ -11832,7 +11832,7 @@
       </c>
       <c r="B121" s="59" t="inlineStr">
         <is>
-          <t>רותם דרור</t>
+          <t>שחר קרן</t>
         </is>
       </c>
       <c r="C121" s="60" t="inlineStr">
@@ -11855,7 +11855,7 @@
       </c>
       <c r="B122" s="59" t="inlineStr">
         <is>
-          <t>שירה ספונוב</t>
+          <t>תמר פרידמן</t>
         </is>
       </c>
       <c r="C122" s="60" t="inlineStr">
@@ -11878,7 +11878,7 @@
       </c>
       <c r="B123" s="59" t="inlineStr">
         <is>
-          <t>תמר פרידמן</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C123" s="60" t="inlineStr">
@@ -11888,11 +11888,11 @@
       </c>
       <c r="D123" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב מוצ"ש</t>
+          <t>ניקיון בית המדרש במוצ"ש</t>
         </is>
       </c>
       <c r="E123" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="124">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="B124" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>אוריה תעשה</t>
         </is>
       </c>
       <c r="C124" s="60" t="inlineStr">
@@ -11924,7 +11924,7 @@
       </c>
       <c r="B125" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C125" s="60" t="inlineStr">
@@ -11947,7 +11947,7 @@
       </c>
       <c r="B126" s="59" t="inlineStr">
         <is>
-          <t>יערה ריס</t>
+          <t>חיים שמאי</t>
         </is>
       </c>
       <c r="C126" s="60" t="inlineStr">
@@ -11970,7 +11970,7 @@
       </c>
       <c r="B127" s="59" t="inlineStr">
         <is>
-          <t>מאיה פקטר</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C127" s="60" t="inlineStr">
@@ -11993,7 +11993,7 @@
       </c>
       <c r="B128" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="C128" s="60" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="B129" s="59" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C129" s="60" t="inlineStr">
@@ -12039,7 +12039,7 @@
       </c>
       <c r="B130" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C130" s="60" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="B131" s="59" t="inlineStr">
         <is>
-          <t>עמית סיילס</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C131" s="60" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="B132" s="59" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק</t>
+          <t>שירה ספונוב</t>
         </is>
       </c>
       <c r="C132" s="60" t="inlineStr">
@@ -12108,7 +12108,7 @@
       </c>
       <c r="B133" s="59" t="inlineStr">
         <is>
-          <t>שילת פילפל</t>
+          <t>איתמר אסנהיים</t>
         </is>
       </c>
       <c r="C133" s="60" t="inlineStr">
@@ -12118,11 +12118,11 @@
       </c>
       <c r="D133" s="59" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש במוצ"ש</t>
+          <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
       <c r="E133" s="60" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="B134" s="59" t="inlineStr">
         <is>
-          <t>אחיה נחמני</t>
+          <t>איתן וינסטון</t>
         </is>
       </c>
       <c r="C134" s="60" t="inlineStr">
@@ -12154,7 +12154,7 @@
       </c>
       <c r="B135" s="59" t="inlineStr">
         <is>
-          <t>אלה גוטליב</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C135" s="60" t="inlineStr">
@@ -12177,7 +12177,7 @@
       </c>
       <c r="B136" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C136" s="60" t="inlineStr">
@@ -12200,7 +12200,7 @@
       </c>
       <c r="B137" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C137" s="60" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="B138" s="59" t="inlineStr">
         <is>
-          <t>זואי כהן</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C138" s="60" t="inlineStr">
@@ -12246,7 +12246,7 @@
       </c>
       <c r="B139" s="59" t="inlineStr">
         <is>
-          <t>חיים שמאי</t>
+          <t>מאיה פקטר</t>
         </is>
       </c>
       <c r="C139" s="60" t="inlineStr">
@@ -12269,7 +12269,7 @@
       </c>
       <c r="B140" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>נדב טוקר</t>
         </is>
       </c>
       <c r="C140" s="60" t="inlineStr">
@@ -12292,7 +12292,7 @@
       </c>
       <c r="B141" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>עמית סיילס</t>
         </is>
       </c>
       <c r="C141" s="60" t="inlineStr">
@@ -12315,7 +12315,7 @@
       </c>
       <c r="B142" s="59" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>עמית שי אברהם</t>
         </is>
       </c>
       <c r="C142" s="60" t="inlineStr">
@@ -12338,7 +12338,7 @@
       </c>
       <c r="B143" s="59" t="inlineStr">
         <is>
-          <t>נדב טוקר</t>
+          <t>רועי צבי סרי</t>
         </is>
       </c>
       <c r="C143" s="60" t="inlineStr">
@@ -12361,7 +12361,7 @@
       </c>
       <c r="B144" s="59" t="inlineStr">
         <is>
-          <t>רועי צבי סרי</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C144" s="60" t="inlineStr">
@@ -12384,21 +12384,21 @@
       </c>
       <c r="B145" s="59" t="inlineStr">
         <is>
-          <t>שחר קרן</t>
+          <t>יונתן לירז</t>
         </is>
       </c>
       <c r="C145" s="60" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
+          <t>תורנות שבת</t>
         </is>
       </c>
       <c r="D145" s="59" t="inlineStr">
         <is>
-          <t>ניקיון חדר האוכל במוצ"ש</t>
+          <t>ארוחת ערב</t>
         </is>
       </c>
       <c r="E145" s="60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -12407,7 +12407,7 @@
       </c>
       <c r="B146" s="59" t="inlineStr">
         <is>
-          <t>יונתן לירז</t>
+          <t>מעיין יוספי</t>
         </is>
       </c>
       <c r="C146" s="60" t="inlineStr">
@@ -12430,7 +12430,7 @@
       </c>
       <c r="B147" s="59" t="inlineStr">
         <is>
-          <t>ינון לוי</t>
+          <t>מעיין רחל דינר</t>
         </is>
       </c>
       <c r="C147" s="60" t="inlineStr">
@@ -12453,7 +12453,7 @@
       </c>
       <c r="B148" s="59" t="inlineStr">
         <is>
-          <t>מעיין יוספי</t>
+          <t>ניתאי שלום</t>
         </is>
       </c>
       <c r="C148" s="60" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="B149" s="59" t="inlineStr">
         <is>
-          <t>ניתאי שלום</t>
+          <t>אלרואי גרינברג</t>
         </is>
       </c>
       <c r="C149" s="60" t="inlineStr">
@@ -12486,7 +12486,7 @@
       </c>
       <c r="D149" s="59" t="inlineStr">
         <is>
-          <t>ארוחת ערב</t>
+          <t>ארוחת צהריים שבת</t>
         </is>
       </c>
       <c r="E149" s="60" t="n">
@@ -12522,7 +12522,7 @@
       </c>
       <c r="B151" s="59" t="inlineStr">
         <is>
-          <t>הדר עמדי</t>
+          <t>רגב שהם</t>
         </is>
       </c>
       <c r="C151" s="60" t="inlineStr">
@@ -12545,7 +12545,7 @@
       </c>
       <c r="B152" s="59" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר</t>
+          <t>רוני כהן</t>
         </is>
       </c>
       <c r="C152" s="60" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="B153" s="59" t="inlineStr">
         <is>
-          <t>רגב שהם</t>
+          <t>אלה מאיר</t>
         </is>
       </c>
       <c r="C153" s="60" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="D153" s="59" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שבת</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E153" s="60" t="n">
@@ -12591,7 +12591,7 @@
       </c>
       <c r="B154" s="59" t="inlineStr">
         <is>
-          <t>הילי אלפסי</t>
+          <t>שילת פילפל</t>
         </is>
       </c>
       <c r="C154" s="60" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B155" s="59" t="inlineStr">
         <is>
-          <t>שילת פילפל</t>
+          <t>אוריה תעשה</t>
         </is>
       </c>
       <c r="C155" s="60" t="inlineStr">
@@ -12624,11 +12624,11 @@
       </c>
       <c r="D155" s="59" t="inlineStr">
         <is>
-          <t>גסטרונומים</t>
+          <t>טיש</t>
         </is>
       </c>
       <c r="E155" s="60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="156">
@@ -12637,7 +12637,7 @@
       </c>
       <c r="B156" s="59" t="inlineStr">
         <is>
-          <t>משה אוברשטיין</t>
+          <t>ארבל פרנקו</t>
         </is>
       </c>
       <c r="C156" s="60" t="inlineStr">
@@ -12660,7 +12660,7 @@
       </c>
       <c r="B157" s="59" t="inlineStr">
         <is>
-          <t>נגה שוהם</t>
+          <t>נדב טוקר</t>
         </is>
       </c>
       <c r="C157" s="60" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="B158" s="59" t="inlineStr">
         <is>
-          <t>נדב טוקר</t>
+          <t>אביה וייל</t>
         </is>
       </c>
       <c r="C158" s="60" t="inlineStr">
@@ -12693,11 +12693,11 @@
       </c>
       <c r="D158" s="59" t="inlineStr">
         <is>
-          <t>טיש</t>
+          <t>פינוי ארוחת ערב</t>
         </is>
       </c>
       <c r="E158" s="60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="159">
@@ -12706,7 +12706,7 @@
       </c>
       <c r="B159" s="59" t="inlineStr">
         <is>
-          <t>אביה וייל</t>
+          <t>יואב אוחנה</t>
         </is>
       </c>
       <c r="C159" s="60" t="inlineStr">
@@ -12729,7 +12729,7 @@
       </c>
       <c r="B160" s="59" t="inlineStr">
         <is>
-          <t>ארבל פרנקו</t>
+          <t>יובל יצחק</t>
         </is>
       </c>
       <c r="C160" s="60" t="inlineStr">
@@ -12752,7 +12752,7 @@
       </c>
       <c r="B161" s="59" t="inlineStr">
         <is>
-          <t>יואב אוחנה</t>
+          <t>ינון לוי</t>
         </is>
       </c>
       <c r="C161" s="60" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="B163" s="59" t="inlineStr">
         <is>
-          <t>שחר מרקוביץ' גליק</t>
+          <t>אחיה נחמני</t>
         </is>
       </c>
       <c r="C163" s="60" t="inlineStr">
@@ -12808,7 +12808,7 @@
       </c>
       <c r="D163" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת ערב</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E163" s="60" t="n">
@@ -12821,7 +12821,7 @@
       </c>
       <c r="B164" s="59" t="inlineStr">
         <is>
-          <t>איתמר אסנהיים</t>
+          <t>הדר עמדי</t>
         </is>
       </c>
       <c r="C164" s="60" t="inlineStr">
@@ -12844,7 +12844,7 @@
       </c>
       <c r="B165" s="59" t="inlineStr">
         <is>
-          <t>איתן וינסטון</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C165" s="60" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="B166" s="59" t="inlineStr">
         <is>
-          <t>עמית שי אברהם</t>
+          <t>נגה שוהם</t>
         </is>
       </c>
       <c r="C166" s="60" t="inlineStr">
@@ -12913,7 +12913,7 @@
       </c>
       <c r="B168" s="59" t="inlineStr">
         <is>
-          <t>רוני כהן</t>
+          <t>הלל פינגולד</t>
         </is>
       </c>
       <c r="C168" s="60" t="inlineStr">
@@ -12923,11 +12923,11 @@
       </c>
       <c r="D168" s="59" t="inlineStr">
         <is>
-          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="E168" s="60" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="169">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="B169" s="59" t="inlineStr">
         <is>
-          <t>אלרואי גרינברג</t>
+          <t>ליבי בוכריס</t>
         </is>
       </c>
       <c r="C169" s="60" t="inlineStr">
@@ -12959,7 +12959,7 @@
       </c>
       <c r="B170" s="59" t="inlineStr">
         <is>
-          <t>הלל פינגולד</t>
+          <t>ניצן גמלא</t>
         </is>
       </c>
       <c r="C170" s="60" t="inlineStr">
@@ -12982,21 +12982,21 @@
       </c>
       <c r="B171" s="59" t="inlineStr">
         <is>
-          <t>ניצן גמלא</t>
+          <t>הילי אלפסי</t>
         </is>
       </c>
       <c r="C171" s="60" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="D171" s="59" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E171" s="60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="172">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="B172" s="59" t="inlineStr">
         <is>
-          <t>אוריה תעשה</t>
+          <t>זואי כהן</t>
         </is>
       </c>
       <c r="C172" s="60" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="B173" s="59" t="inlineStr">
         <is>
-          <t>איתי בן מנחם</t>
+          <t>טליה קור</t>
         </is>
       </c>
       <c r="C173" s="60" t="inlineStr">
@@ -13051,7 +13051,7 @@
       </c>
       <c r="B174" s="59" t="inlineStr">
         <is>
-          <t>איתן כהן</t>
+          <t>יהב לוי</t>
         </is>
       </c>
       <c r="C174" s="60" t="inlineStr">
@@ -13074,7 +13074,7 @@
       </c>
       <c r="B175" s="59" t="inlineStr">
         <is>
-          <t>אלה מאיר</t>
+          <t>יערה ריס</t>
         </is>
       </c>
       <c r="C175" s="60" t="inlineStr">
@@ -13097,7 +13097,7 @@
       </c>
       <c r="B176" s="59" t="inlineStr">
         <is>
-          <t>אנה עזריאל</t>
+          <t>כליל בלאוקופף</t>
         </is>
       </c>
       <c r="C176" s="60" t="inlineStr">
@@ -13120,7 +13120,7 @@
       </c>
       <c r="B177" s="59" t="inlineStr">
         <is>
-          <t>הילה לביא</t>
+          <t>נבו בלוך</t>
         </is>
       </c>
       <c r="C177" s="60" t="inlineStr">
@@ -13143,7 +13143,7 @@
       </c>
       <c r="B178" s="59" t="inlineStr">
         <is>
-          <t>טליה קור</t>
+          <t>עופר בביוף</t>
         </is>
       </c>
       <c r="C178" s="60" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="B179" s="59" t="inlineStr">
         <is>
-          <t>יובל יצחק</t>
+          <t>רוני פרנקל</t>
         </is>
       </c>
       <c r="C179" s="60" t="inlineStr">
@@ -13189,7 +13189,7 @@
       </c>
       <c r="B180" s="59" t="inlineStr">
         <is>
-          <t>רוני פרנקל</t>
+          <t>שחר מרקוביץ' גליק</t>
         </is>
       </c>
       <c r="C180" s="60" t="inlineStr">
@@ -13212,7 +13212,7 @@
       </c>
       <c r="B181" s="59" t="inlineStr">
         <is>
-          <t>תמר פרידמן</t>
+          <t>שירה ספונוב</t>
         </is>
       </c>
       <c r="C181" s="60" t="inlineStr">
@@ -13235,7 +13235,7 @@
       </c>
       <c r="B182" s="59" t="inlineStr">
         <is>
-          <t>תמר פרימור</t>
+          <t>תמר פרידמן</t>
         </is>
       </c>
       <c r="C182" s="60" t="inlineStr">
@@ -13258,7 +13258,7 @@
       </c>
       <c r="B183" s="59" t="inlineStr">
         <is>
-          <t>יהב לוי</t>
+          <t>איתי בן מנחם</t>
         </is>
       </c>
       <c r="C183" s="60" t="inlineStr">
@@ -13281,7 +13281,7 @@
       </c>
       <c r="B184" s="59" t="inlineStr">
         <is>
-          <t>ירדן בן שחר</t>
+          <t>אנה עזריאל</t>
         </is>
       </c>
       <c r="C184" s="60" t="inlineStr">
@@ -13304,7 +13304,7 @@
       </c>
       <c r="B185" s="59" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף</t>
+          <t>ירדן בן שחר</t>
         </is>
       </c>
       <c r="C185" s="60" t="inlineStr">
@@ -13327,7 +13327,7 @@
       </c>
       <c r="B186" s="59" t="inlineStr">
         <is>
-          <t>נגה חוה כהן</t>
+          <t>משה אוברשטיין</t>
         </is>
       </c>
       <c r="C186" s="60" t="inlineStr">
@@ -13350,7 +13350,7 @@
       </c>
       <c r="B187" s="59" t="inlineStr">
         <is>
-          <t>נועם ישראל קומפאס</t>
+          <t>נגה חוה כהן</t>
         </is>
       </c>
       <c r="C187" s="60" t="inlineStr">
@@ -13373,7 +13373,7 @@
       </c>
       <c r="B188" s="59" t="inlineStr">
         <is>
-          <t>עופר בביוף</t>
+          <t>נועם ישראל קומפאס</t>
         </is>
       </c>
       <c r="C188" s="60" t="inlineStr">
@@ -13396,7 +13396,7 @@
       </c>
       <c r="B189" s="59" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין</t>
+          <t>תמר פרימור</t>
         </is>
       </c>
       <c r="C189" s="60" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="C12" s="53" t="inlineStr">
         <is>
-          <t>6 עוגות אינגליש קייק</t>
+          <t>12 עוגות אינגליש קייק</t>
         </is>
       </c>
       <c r="D12" s="21" t="inlineStr">
@@ -14914,7 +14914,7 @@
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>חצי מהמטבוחה, חצי מסלט החצילים וחצי מהחלות</t>
+          <t>חצי מהמטבוחה, חצי סלט חצילים וחצי חלות</t>
         </is>
       </c>
       <c r="C21" s="53" t="n"/>
@@ -14928,33 +14928,69 @@
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>שאר המטבוחה, סלט החצילים והחלות</t>
+          <t>חצי מהמטבוחה, חצי סלט חצילים וחצי חלות</t>
         </is>
       </c>
       <c r="C22" s="53" t="n"/>
       <c r="D22" s="21" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="53" t="n"/>
-      <c r="B23" s="48" t="n"/>
+      <c r="A23" s="53" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>3 פסי עוגת שוקולד, 3 פסי עוגת שמרים</t>
+        </is>
+      </c>
       <c r="C23" s="53" t="n"/>
       <c r="D23" s="21" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="53" t="n"/>
-      <c r="B24" s="48" t="n"/>
+      <c r="A24" s="53" t="inlineStr">
+        <is>
+          <t>קידוש</t>
+        </is>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>5 פסי עוגת שוקולד, 5 פסי עוגת שמרים</t>
+        </is>
+      </c>
       <c r="C24" s="53" t="n"/>
       <c r="D24" s="21" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="53" t="n"/>
-      <c r="B25" s="48" t="n"/>
+      <c r="A25" s="53" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>ג'חנון, רסק עגבניות וביצים (מהקייטרינג)</t>
+        </is>
+      </c>
       <c r="C25" s="53" t="n"/>
-      <c r="D25" s="21" t="n"/>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>הערה מהטופס</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" s="53" t="n"/>
-      <c r="B26" s="48" t="n"/>
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>סעודה שלישית</t>
+        </is>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>4 פסי עוגת שוקולד, 4 פסי עוגת שמרים</t>
+        </is>
+      </c>
       <c r="C26" s="53" t="n"/>
       <c r="D26" s="21" t="n"/>
     </row>

--- a/shabbatot/2026-10-16.xlsx
+++ b/shabbatot/2026-10-16.xlsx
@@ -2376,39 +2376,37 @@
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="53" t="inlineStr">
         <is>
-          <t>הכנות שישי</t>
-        </is>
-      </c>
-      <c r="B13" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B13" s="57" t="inlineStr">
+        <is>
+          <t>שבת</t>
         </is>
       </c>
       <c r="C13" s="55" t="n">
-        <v>0.5</v>
+        <v>0.6875</v>
       </c>
       <c r="D13" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים שישי</t>
+          <t>גסטרונומים</t>
         </is>
       </c>
       <c r="E13" s="21" t="inlineStr">
         <is>
-          <t>הגשת ארוחת הצהריים</t>
-        </is>
-      </c>
-      <c r="F13" s="53" t="n">
-        <v>2</v>
-      </c>
+          <t>הכנסת הג'חנון (מהקייטרינג) לתנור החימום — לסעודה שלישית</t>
+        </is>
+      </c>
+      <c r="F13" s="53" t="n"/>
       <c r="G13" s="31" t="inlineStr">
         <is>
-          <t>של״ו רובינשטיין, עמית סיילס</t>
+          <t>אלה מאיר, שילת פילפל</t>
         </is>
       </c>
       <c r="H13" s="48" t="n"/>
       <c r="I13" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>סעודה שלישית</t>
         </is>
       </c>
       <c r="J13" s="21" t="n"/>
@@ -2425,7 +2423,7 @@
         </is>
       </c>
       <c r="C14" s="55" t="n">
-        <v>0.5416666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="D14" s="48" t="inlineStr">
         <is>
@@ -2434,7 +2432,7 @@
       </c>
       <c r="E14" s="21" t="inlineStr">
         <is>
-          <t>קיפול הארוחה, שטיפת כלים</t>
+          <t>הגשת ארוחת הצהריים</t>
         </is>
       </c>
       <c r="F14" s="53" t="n">
@@ -2442,7 +2440,7 @@
       </c>
       <c r="G14" s="31" t="inlineStr">
         <is>
-          <t>עמית שי אברהם, אחיה נחמני</t>
+          <t>של״ו רובינשטיין, עמית סיילס</t>
         </is>
       </c>
       <c r="H14" s="48" t="n"/>
@@ -2453,26 +2451,66 @@
       </c>
       <c r="J14" s="21" t="n"/>
     </row>
-    <row r="15" ht="105" customHeight="1">
+    <row r="15" ht="30" customHeight="1">
       <c r="A15" s="53" t="inlineStr">
         <is>
+          <t>הכנות שישי</t>
+        </is>
+      </c>
+      <c r="B15" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C15" s="55" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="D15" s="48" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים שישי</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="inlineStr">
+        <is>
+          <t>קיפול הארוחה, שטיפת כלים</t>
+        </is>
+      </c>
+      <c r="F15" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>עמית שי אברהם, אחיה נחמני</t>
+        </is>
+      </c>
+      <c r="H15" s="48" t="n"/>
+      <c r="I15" s="48" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="n"/>
+    </row>
+    <row r="16" ht="105" customHeight="1">
+      <c r="A16" s="53" t="inlineStr">
+        <is>
           <t>תורנות שישי</t>
         </is>
       </c>
-      <c r="B15" s="54" t="inlineStr">
+      <c r="B16" s="54" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="C15" s="55" t="n">
+      <c r="C16" s="55" t="n">
         <v>0.3333333333333333</v>
       </c>
-      <c r="D15" s="48" t="inlineStr">
+      <c r="D16" s="48" t="inlineStr">
         <is>
           <t>בית מדרש</t>
         </is>
       </c>
-      <c r="E15" s="21" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>סידור בית המדרש:
 טאטוא ושטיפת הרצפה
@@ -2483,52 +2521,12 @@
 הנחת סידורים על הכסאות</t>
         </is>
       </c>
-      <c r="F15" s="53" t="n">
+      <c r="F16" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G15" s="31" t="inlineStr">
+      <c r="G16" s="31" t="inlineStr">
         <is>
           <t>יהב לוי, זואי כהן, שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן, הילי אלפסי, כליל בלאוקופף, רוני פרנקל, נבו בלוך, טליה קור</t>
-        </is>
-      </c>
-      <c r="H15" s="48" t="n"/>
-      <c r="I15" s="48" t="inlineStr">
-        <is>
-          <t>תחילת עבודה</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="n"/>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שישי</t>
-        </is>
-      </c>
-      <c r="B16" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C16" s="55" t="n">
-        <v>0.3645833333333333</v>
-      </c>
-      <c r="D16" s="48" t="inlineStr">
-        <is>
-          <t>בית מדרש</t>
-        </is>
-      </c>
-      <c r="E16" s="21" t="inlineStr">
-        <is>
-          <t>עזרה בהכנת חלות</t>
-        </is>
-      </c>
-      <c r="F16" s="53" t="n">
-        <v>5</v>
-      </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t>שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן</t>
         </is>
       </c>
       <c r="H16" s="48" t="n"/>
@@ -2560,15 +2558,15 @@
       </c>
       <c r="E17" s="21" t="inlineStr">
         <is>
-          <t>עזרה בהכנת בראוניז ללא גלוטן</t>
+          <t>עזרה בהכנת חלות</t>
         </is>
       </c>
       <c r="F17" s="53" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G17" s="31" t="inlineStr">
         <is>
-          <t>יהב לוי, הילי אלפסי</t>
+          <t>שירה ספונוב, יערה ריס, שחר מרקוביץ' גליק, עופר בביוף, תמר פרידמן</t>
         </is>
       </c>
       <c r="H17" s="48" t="n"/>
@@ -2600,15 +2598,15 @@
       </c>
       <c r="E18" s="21" t="inlineStr">
         <is>
-          <t>עזרה בהכנת עוגת שמרים</t>
+          <t>עזרה בהכנת בראוניז ללא גלוטן</t>
         </is>
       </c>
       <c r="F18" s="53" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G18" s="31" t="inlineStr">
         <is>
-          <t>כליל בלאוקופף, רוני פרנקל, נבו בלוך</t>
+          <t>יהב לוי, הילי אלפסי</t>
         </is>
       </c>
       <c r="H18" s="48" t="n"/>
@@ -2640,15 +2638,15 @@
       </c>
       <c r="E19" s="21" t="inlineStr">
         <is>
-          <t>עזרה בהכנת סלט חצילים</t>
+          <t>עזרה בהכנת עוגת שמרים</t>
         </is>
       </c>
       <c r="F19" s="53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G19" s="31" t="inlineStr">
         <is>
-          <t>זואי כהן, טליה קור</t>
+          <t>כליל בלאוקופף, רוני פרנקל, נבו בלוך</t>
         </is>
       </c>
       <c r="H19" s="48" t="n"/>
@@ -2662,7 +2660,7 @@
     <row r="20" ht="30" customHeight="1">
       <c r="A20" s="53" t="inlineStr">
         <is>
-          <t>תורנות שבת</t>
+          <t>תורנות שישי</t>
         </is>
       </c>
       <c r="B20" s="54" t="inlineStr">
@@ -2671,16 +2669,16 @@
         </is>
       </c>
       <c r="C20" s="55" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="D20" s="48" t="inlineStr">
         <is>
-          <t>גסטרונומים</t>
+          <t>בית מדרש</t>
         </is>
       </c>
       <c r="E20" s="21" t="inlineStr">
         <is>
-          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
+          <t>עזרה בהכנת סלט חצילים</t>
         </is>
       </c>
       <c r="F20" s="53" t="n">
@@ -2688,13 +2686,13 @@
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>אלה מאיר, שילת פילפל</t>
+          <t>זואי כהן, טליה קור</t>
         </is>
       </c>
       <c r="H20" s="48" t="n"/>
       <c r="I20" s="48" t="inlineStr">
         <is>
-          <t>הדלקת נרות</t>
+          <t>תחילת עבודה</t>
         </is>
       </c>
       <c r="J20" s="21" t="n"/>
@@ -2711,59 +2709,59 @@
         </is>
       </c>
       <c r="C21" s="55" t="n">
+        <v>0.5833333333333334</v>
+      </c>
+      <c r="D21" s="48" t="inlineStr">
+        <is>
+          <t>גסטרונומים</t>
+        </is>
+      </c>
+      <c r="E21" s="21" t="inlineStr">
+        <is>
+          <t>פריקת האוכל למקרר — אוכל ארוחת צהריים שבת: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
+        </is>
+      </c>
+      <c r="F21" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>אלה מאיר, שילת פילפל</t>
+        </is>
+      </c>
+      <c r="H21" s="48" t="n"/>
+      <c r="I21" s="48" t="inlineStr">
+        <is>
+          <t>הדלקת נרות</t>
+        </is>
+      </c>
+      <c r="J21" s="21" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="53" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B22" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C22" s="55" t="n">
         <v>0.6944444444444444</v>
       </c>
-      <c r="D21" s="48" t="inlineStr">
+      <c r="D22" s="48" t="inlineStr">
         <is>
           <t>גסטרונומים</t>
         </is>
       </c>
-      <c r="E21" s="21" t="inlineStr">
+      <c r="E22" s="21" t="inlineStr">
         <is>
           <t>הכנסת הגסטרונומים של ארוחת הערב מהמקרר לתנור החימום: כרעיים בגריל, אורז עם אטריות, אפונה וגזר, פלפל ממולא (טבעוני)
 חיבור המיחמים בפינת הקפה</t>
         </is>
       </c>
-      <c r="F21" s="53" t="n">
-        <v>2</v>
-      </c>
-      <c r="G21" s="31" t="inlineStr">
-        <is>
-          <t>אלה מאיר, שילת פילפל</t>
-        </is>
-      </c>
-      <c r="H21" s="48" t="n"/>
-      <c r="I21" s="48" t="inlineStr">
-        <is>
-          <t>הדלקת נרות</t>
-        </is>
-      </c>
-      <c r="J21" s="21" t="n"/>
-    </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B22" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C22" s="55" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="D22" s="48" t="inlineStr">
-        <is>
-          <t>גסטרונומים</t>
-        </is>
-      </c>
-      <c r="E22" s="21" t="inlineStr">
-        <is>
-          <t>הוצאת הגסטרונומים של ארוחת הערב מתנור החימום לשולחן ההגשה</t>
-        </is>
-      </c>
       <c r="F22" s="53" t="n">
         <v>2</v>
       </c>
@@ -2775,7 +2773,7 @@
       <c r="H22" s="48" t="n"/>
       <c r="I22" s="48" t="inlineStr">
         <is>
-          <t>סעודת שבת</t>
+          <t>הדלקת נרות</t>
         </is>
       </c>
       <c r="J22" s="21" t="n"/>
@@ -2786,13 +2784,13 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B23" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
+      <c r="B23" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
         </is>
       </c>
       <c r="C23" s="55" t="n">
-        <v>0.4583333333333333</v>
+        <v>0.8125</v>
       </c>
       <c r="D23" s="48" t="inlineStr">
         <is>
@@ -2801,7 +2799,7 @@
       </c>
       <c r="E23" s="21" t="inlineStr">
         <is>
-          <t>הכנסת האוכל של ארוחת הצהריים לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
+          <t>הוצאת הגסטרונומים של ארוחת הערב מתנור החימום לשולחן ההגשה</t>
         </is>
       </c>
       <c r="F23" s="53" t="n">
@@ -2815,7 +2813,7 @@
       <c r="H23" s="48" t="n"/>
       <c r="I23" s="48" t="inlineStr">
         <is>
-          <t>קידוש</t>
+          <t>סעודת שבת</t>
         </is>
       </c>
       <c r="J23" s="21" t="n"/>
@@ -2832,7 +2830,7 @@
         </is>
       </c>
       <c r="C24" s="55" t="n">
-        <v>0.5520833333333334</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="D24" s="48" t="inlineStr">
         <is>
@@ -2841,7 +2839,7 @@
       </c>
       <c r="E24" s="21" t="inlineStr">
         <is>
-          <t>הוצאת הגסטרונומים של ארוחת הצהריים מתנור החימום לשולחן ההגשה</t>
+          <t>הכנסת האוכל של ארוחת הצהריים לתנור החימום: כתף בקר, אורז לבן, תפו"א ובטטה, שעועית ירוקה מוקפצת, מוקפץ (טבעוני)</t>
         </is>
       </c>
       <c r="F24" s="53" t="n">
@@ -2855,7 +2853,7 @@
       <c r="H24" s="48" t="n"/>
       <c r="I24" s="48" t="inlineStr">
         <is>
-          <t>ארוחת צהריים</t>
+          <t>קידוש</t>
         </is>
       </c>
       <c r="J24" s="21" t="n"/>
@@ -2866,64 +2864,104 @@
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B25" s="54" t="inlineStr">
+      <c r="B25" s="57" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C25" s="55" t="n">
+        <v>0.5520833333333334</v>
+      </c>
+      <c r="D25" s="48" t="inlineStr">
+        <is>
+          <t>גסטרונומים</t>
+        </is>
+      </c>
+      <c r="E25" s="21" t="inlineStr">
+        <is>
+          <t>הוצאת הגסטרונומים של ארוחת הצהריים מתנור החימום לשולחן ההגשה</t>
+        </is>
+      </c>
+      <c r="F25" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>אלה מאיר, שילת פילפל</t>
+        </is>
+      </c>
+      <c r="H25" s="48" t="n"/>
+      <c r="I25" s="48" t="inlineStr">
+        <is>
+          <t>ארוחת צהריים</t>
+        </is>
+      </c>
+      <c r="J25" s="21" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="53" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B26" s="54" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="C25" s="55" t="n">
+      <c r="C26" s="55" t="n">
         <v>0.78125</v>
       </c>
-      <c r="D25" s="48" t="inlineStr">
+      <c r="D26" s="48" t="inlineStr">
         <is>
           <t>ארוחת ערב</t>
         </is>
       </c>
-      <c r="E25" s="21" t="inlineStr">
+      <c r="E26" s="21" t="inlineStr">
         <is>
           <t>הכנת סלט כרוב מרענן, סלט טחינה ביתית</t>
         </is>
       </c>
-      <c r="F25" s="53" t="n">
+      <c r="F26" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="G25" s="31" t="inlineStr">
+      <c r="G26" s="31" t="inlineStr">
         <is>
           <t>מעיין רחל דינר, יונתן לירז, מעיין יוספי</t>
         </is>
       </c>
-      <c r="H25" s="48" t="inlineStr">
+      <c r="H26" s="48" t="inlineStr">
         <is>
           <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
         </is>
       </c>
-      <c r="I25" s="48" t="inlineStr">
+      <c r="I26" s="48" t="inlineStr">
         <is>
           <t>סעודת שבת</t>
         </is>
       </c>
-      <c r="J25" s="21" t="n"/>
-    </row>
-    <row r="26" ht="60" customHeight="1">
-      <c r="A26" s="53" t="inlineStr">
+      <c r="J26" s="21" t="n"/>
+    </row>
+    <row r="27" ht="60" customHeight="1">
+      <c r="A27" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B26" s="54" t="inlineStr">
+      <c r="B27" s="54" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="C26" s="55" t="n">
+      <c r="C27" s="55" t="n">
         <v>0.7916666666666666</v>
       </c>
-      <c r="D26" s="48" t="inlineStr">
+      <c r="D27" s="48" t="inlineStr">
         <is>
           <t>ארוחת ערב</t>
         </is>
       </c>
-      <c r="E26" s="21" t="inlineStr">
+      <c r="E27" s="21" t="inlineStr">
         <is>
           <t>עריכת השולחן:
 סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס
@@ -2931,42 +2969,42 @@
 צלחות וסכו"ם</t>
         </is>
       </c>
-      <c r="F26" s="53" t="n">
+      <c r="F27" s="53" t="n">
         <v>4</v>
       </c>
-      <c r="G26" s="31" t="inlineStr">
+      <c r="G27" s="31" t="inlineStr">
         <is>
           <t>ניתאי שלום, מעיין רחל דינר, יונתן לירז, מעיין יוספי</t>
         </is>
       </c>
-      <c r="H26" s="48" t="n"/>
-      <c r="I26" s="48" t="inlineStr">
+      <c r="H27" s="48" t="n"/>
+      <c r="I27" s="48" t="inlineStr">
         <is>
           <t>סעודת שבת</t>
         </is>
       </c>
-      <c r="J26" s="21" t="n"/>
-    </row>
-    <row r="27" ht="90" customHeight="1">
-      <c r="A27" s="53" t="inlineStr">
+      <c r="J27" s="21" t="n"/>
+    </row>
+    <row r="28" ht="90" customHeight="1">
+      <c r="A28" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B27" s="54" t="inlineStr">
+      <c r="B28" s="54" t="inlineStr">
         <is>
           <t>שישי</t>
         </is>
       </c>
-      <c r="C27" s="55" t="n">
+      <c r="C28" s="55" t="n">
         <v>0.8541666666666666</v>
       </c>
-      <c r="D27" s="48" t="inlineStr">
+      <c r="D28" s="48" t="inlineStr">
         <is>
           <t>פינוי ארוחת ערב</t>
         </is>
       </c>
-      <c r="E27" s="21" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>פינוי הארוחה:
 האוכל שנשאר — למקרר
@@ -2976,45 +3014,9 @@
 טאטוא</t>
         </is>
       </c>
-      <c r="F27" s="53" t="n">
+      <c r="F28" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G27" s="31" t="inlineStr">
-        <is>
-          <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
-        </is>
-      </c>
-      <c r="H27" s="48" t="n"/>
-      <c r="I27" s="48" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="J27" s="21" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B28" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C28" s="55" t="n"/>
-      <c r="D28" s="48" t="inlineStr">
-        <is>
-          <t>פינוי ארוחת ערב</t>
-        </is>
-      </c>
-      <c r="E28" s="21" t="inlineStr">
-        <is>
-          <t>שטיפת הגסטרונומים בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="F28" s="53" t="n"/>
       <c r="G28" s="31" t="inlineStr">
         <is>
           <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
@@ -3028,7 +3030,7 @@
       </c>
       <c r="J28" s="21" t="n"/>
     </row>
-    <row r="29" ht="60" customHeight="1">
+    <row r="29" ht="30" customHeight="1">
       <c r="A29" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
@@ -3039,15 +3041,51 @@
           <t>שישי</t>
         </is>
       </c>
-      <c r="C29" s="55" t="n">
+      <c r="C29" s="55" t="n"/>
+      <c r="D29" s="48" t="inlineStr">
+        <is>
+          <t>פינוי ארוחת ערב</t>
+        </is>
+      </c>
+      <c r="E29" s="21" t="inlineStr">
+        <is>
+          <t>שטיפת הגסטרונומים בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F29" s="53" t="n"/>
+      <c r="G29" s="31" t="inlineStr">
+        <is>
+          <t>ינון לוי, אביה וייל, יואב אוחנה, יובל יצחק, רועי צבי סרי</t>
+        </is>
+      </c>
+      <c r="H29" s="48" t="n"/>
+      <c r="I29" s="48" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="J29" s="21" t="n"/>
+    </row>
+    <row r="30" ht="60" customHeight="1">
+      <c r="A30" s="53" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B30" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C30" s="55" t="n">
         <v>0.8541666666666666</v>
       </c>
-      <c r="D29" s="48" t="inlineStr">
+      <c r="D30" s="48" t="inlineStr">
         <is>
           <t>טיש</t>
         </is>
       </c>
-      <c r="E29" s="21" t="inlineStr">
+      <c r="E30" s="21" t="inlineStr">
         <is>
           <t>חימום 3 פסי עוגת שוקולד, 3 פסי עוגת שמרים — הכל פרווה
 חיתוך 10 תפוחים
@@ -3055,45 +3093,9 @@
 פריסת שולחן במרכז: העוגות, גרעינים, חצי מהענבים ו-10 התפוחים</t>
         </is>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F30" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="G29" s="31" t="inlineStr">
-        <is>
-          <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
-        </is>
-      </c>
-      <c r="H29" s="48" t="n"/>
-      <c r="I29" s="48" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="J29" s="21" t="n"/>
-    </row>
-    <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B30" s="54" t="inlineStr">
-        <is>
-          <t>שישי</t>
-        </is>
-      </c>
-      <c r="C30" s="55" t="n"/>
-      <c r="D30" s="48" t="inlineStr">
-        <is>
-          <t>טיש</t>
-        </is>
-      </c>
-      <c r="E30" s="21" t="inlineStr">
-        <is>
-          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
-        </is>
-      </c>
-      <c r="F30" s="53" t="n"/>
       <c r="G30" s="31" t="inlineStr">
         <is>
           <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
@@ -3107,26 +3109,62 @@
       </c>
       <c r="J30" s="21" t="n"/>
     </row>
-    <row r="31" ht="75" customHeight="1">
+    <row r="31" ht="30" customHeight="1">
       <c r="A31" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B31" s="57" t="inlineStr">
+      <c r="B31" s="54" t="inlineStr">
+        <is>
+          <t>שישי</t>
+        </is>
+      </c>
+      <c r="C31" s="55" t="n"/>
+      <c r="D31" s="48" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="E31" s="21" t="inlineStr">
+        <is>
+          <t>טאטוא חדר האוכל וניקוי השולחנות בסיום הטיש</t>
+        </is>
+      </c>
+      <c r="F31" s="53" t="n"/>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>ארבל פרנקו, אוריה תעשה, נדב טוקר</t>
+        </is>
+      </c>
+      <c r="H31" s="48" t="n"/>
+      <c r="I31" s="48" t="inlineStr">
+        <is>
+          <t>טיש</t>
+        </is>
+      </c>
+      <c r="J31" s="21" t="n"/>
+    </row>
+    <row r="32" ht="75" customHeight="1">
+      <c r="A32" s="53" t="inlineStr">
+        <is>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B32" s="57" t="inlineStr">
         <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="C31" s="55" t="n">
+      <c r="C32" s="55" t="n">
         <v>0.4375</v>
       </c>
-      <c r="D31" s="48" t="inlineStr">
+      <c r="D32" s="48" t="inlineStr">
         <is>
           <t>קידוש</t>
         </is>
       </c>
-      <c r="E31" s="21" t="inlineStr">
+      <c r="E32" s="21" t="inlineStr">
         <is>
           <t>סידור וניקיון פינת הקפה — להוציא חלב, למלא קפה וסוכר
 חימום העוגות
@@ -3135,42 +3173,42 @@
 טאטוא הרצפה, סידור כיסאות וארגון המרחב</t>
         </is>
       </c>
-      <c r="F31" s="53" t="n">
+      <c r="F32" s="53" t="n">
         <v>3</v>
       </c>
-      <c r="G31" s="31" t="inlineStr">
+      <c r="G32" s="31" t="inlineStr">
         <is>
           <t>ניצן גמלא, הלל פינגולד, ליבי בוכריס</t>
         </is>
       </c>
-      <c r="H31" s="48" t="n"/>
-      <c r="I31" s="48" t="inlineStr">
+      <c r="H32" s="48" t="n"/>
+      <c r="I32" s="48" t="inlineStr">
         <is>
           <t>קידוש</t>
         </is>
       </c>
-      <c r="J31" s="21" t="n"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
-      <c r="A32" s="53" t="inlineStr">
+      <c r="J32" s="21" t="n"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
+      <c r="A33" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B32" s="57" t="inlineStr">
+      <c r="B33" s="57" t="inlineStr">
         <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="C32" s="55" t="n">
+      <c r="C33" s="55" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="D32" s="48" t="inlineStr">
+      <c r="D33" s="48" t="inlineStr">
         <is>
           <t>ארוחת צהריים שבת</t>
         </is>
       </c>
-      <c r="E32" s="21" t="inlineStr">
+      <c r="E33" s="21" t="inlineStr">
         <is>
           <t>עריכת השולחן:
 הכנת סלט כרוב מרענן, סלט טחינה ביתית
@@ -3178,87 +3216,87 @@
 סלטי קייטרינג: סלק מבושל, כרוב בתחמיץ, בטטה צ'ילי, ירקות מוחמצים, חומוס</t>
         </is>
       </c>
-      <c r="F32" s="53" t="n">
+      <c r="F33" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G32" s="31" t="inlineStr">
+      <c r="G33" s="31" t="inlineStr">
         <is>
           <t>אלרואי גרינברג, בניה מעוז</t>
         </is>
       </c>
-      <c r="H32" s="48" t="inlineStr">
+      <c r="H33" s="48" t="inlineStr">
         <is>
           <t>סלט כרוב מרענן;סלט טחינה ביתית</t>
         </is>
       </c>
-      <c r="I32" s="48" t="inlineStr">
+      <c r="I33" s="48" t="inlineStr">
         <is>
           <t>ארוחת צהריים</t>
         </is>
       </c>
-      <c r="J32" s="21" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="53" t="inlineStr">
+      <c r="J33" s="21" t="n"/>
+    </row>
+    <row r="34" ht="30" customHeight="1">
+      <c r="A34" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B33" s="57" t="inlineStr">
+      <c r="B34" s="57" t="inlineStr">
         <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="C33" s="55" t="n">
+      <c r="C34" s="55" t="n">
         <v>0.5208333333333334</v>
       </c>
-      <c r="D33" s="48" t="inlineStr">
+      <c r="D34" s="48" t="inlineStr">
         <is>
           <t>ארוחת צהריים שבת</t>
         </is>
       </c>
-      <c r="E33" s="21" t="inlineStr">
+      <c r="E34" s="21" t="inlineStr">
         <is>
           <t>כפות הגשה, צלחות וסכו"ם
 סידור שולחנות וכיסאות</t>
         </is>
       </c>
-      <c r="F33" s="53" t="n">
+      <c r="F34" s="53" t="n">
         <v>2</v>
       </c>
-      <c r="G33" s="31" t="inlineStr">
+      <c r="G34" s="31" t="inlineStr">
         <is>
           <t>רגב שהם, רוני כהן</t>
         </is>
       </c>
-      <c r="H33" s="48" t="n"/>
-      <c r="I33" s="48" t="inlineStr">
+      <c r="H34" s="48" t="n"/>
+      <c r="I34" s="48" t="inlineStr">
         <is>
           <t>ארוחת צהריים</t>
         </is>
       </c>
-      <c r="J33" s="21" t="n"/>
-    </row>
-    <row r="34" ht="90" customHeight="1">
-      <c r="A34" s="53" t="inlineStr">
+      <c r="J34" s="21" t="n"/>
+    </row>
+    <row r="35" ht="90" customHeight="1">
+      <c r="A35" s="53" t="inlineStr">
         <is>
           <t>תורנות שבת</t>
         </is>
       </c>
-      <c r="B34" s="57" t="inlineStr">
+      <c r="B35" s="57" t="inlineStr">
         <is>
           <t>שבת</t>
         </is>
       </c>
-      <c r="C34" s="55" t="n">
+      <c r="C35" s="55" t="n">
         <v>0.5833333333333334</v>
       </c>
-      <c r="D34" s="48" t="inlineStr">
+      <c r="D35" s="48" t="inlineStr">
         <is>
           <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
-      <c r="E34" s="21" t="inlineStr">
+      <c r="E35" s="21" t="inlineStr">
         <is>
           <t>פינוי השולחנות:
 האוכל שנשאר — למקרר
@@ -3268,45 +3306,9 @@
 טאטוא</t>
         </is>
       </c>
-      <c r="F34" s="53" t="n">
+      <c r="F35" s="53" t="n">
         <v>5</v>
       </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
-        </is>
-      </c>
-      <c r="H34" s="48" t="n"/>
-      <c r="I34" s="48" t="inlineStr">
-        <is>
-          <t>ארוחת צהריים</t>
-        </is>
-      </c>
-      <c r="J34" s="21" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="53" t="inlineStr">
-        <is>
-          <t>תורנות שבת</t>
-        </is>
-      </c>
-      <c r="B35" s="57" t="inlineStr">
-        <is>
-          <t>שבת</t>
-        </is>
-      </c>
-      <c r="C35" s="55" t="n"/>
-      <c r="D35" s="48" t="inlineStr">
-        <is>
-          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
-        </is>
-      </c>
-      <c r="E35" s="21" t="inlineStr">
-        <is>
-          <t>שטיפת הגסטרונומים בסיום הארוחה</t>
-        </is>
-      </c>
-      <c r="F35" s="53" t="n"/>
       <c r="G35" s="31" t="inlineStr">
         <is>
           <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
@@ -3331,9 +3333,7 @@
           <t>שבת</t>
         </is>
       </c>
-      <c r="C36" s="55" t="n">
-        <v>0.71875</v>
-      </c>
+      <c r="C36" s="55" t="n"/>
       <c r="D36" s="48" t="inlineStr">
         <is>
           <t>פינוי ארוחת צהריים וסעודה שלישית</t>
@@ -3341,21 +3341,19 @@
       </c>
       <c r="E36" s="21" t="inlineStr">
         <is>
-          <t>הוצאת ג'חנון, רסק עגבניות וביצים (מהקייטרינג), 4 פסי עוגת שוקולד, 4 פסי עוגת שמרים לסעודה שלישית</t>
-        </is>
-      </c>
-      <c r="F36" s="53" t="n">
-        <v>2</v>
-      </c>
+          <t>שטיפת הגסטרונומים בסיום הארוחה</t>
+        </is>
+      </c>
+      <c r="F36" s="53" t="n"/>
       <c r="G36" s="31" t="inlineStr">
         <is>
-          <t>הדר עמדי, נגה שוהם</t>
+          <t>הדר עמדי, נגה שוהם, קובי סמייסון, אחיה נחמני, זואי כהן</t>
         </is>
       </c>
       <c r="H36" s="48" t="n"/>
       <c r="I36" s="48" t="inlineStr">
         <is>
-          <t>סעודה שלישית</t>
+          <t>ארוחת צהריים</t>
         </is>
       </c>
       <c r="J36" s="21" t="n"/>
@@ -3363,42 +3361,44 @@
     <row r="37" ht="30" customHeight="1">
       <c r="A37" s="53" t="inlineStr">
         <is>
-          <t>תורנות מוצ"ש</t>
-        </is>
-      </c>
-      <c r="B37" s="56" t="inlineStr">
-        <is>
-          <t>מוצאי שבת</t>
-        </is>
-      </c>
-      <c r="C37" s="55" t="n"/>
+          <t>תורנות שבת</t>
+        </is>
+      </c>
+      <c r="B37" s="57" t="inlineStr">
+        <is>
+          <t>שבת</t>
+        </is>
+      </c>
+      <c r="C37" s="55" t="n">
+        <v>0.71875</v>
+      </c>
       <c r="D37" s="48" t="inlineStr">
         <is>
-          <t>ניקיון בית המדרש במוצ"ש</t>
+          <t>פינוי ארוחת צהריים וסעודה שלישית</t>
         </is>
       </c>
       <c r="E37" s="21" t="inlineStr">
         <is>
-          <t>להחזיר את בית המדרש לקדמותו — השולחנות, הכסאות, המחיצה והסידורים, כמו לפני שבת</t>
+          <t>הוצאת ג'חנון, רסק עגבניות וביצים (מהקייטרינג), 4 פסי עוגת שוקולד, 4 פסי עוגת שמרים לסעודה שלישית</t>
         </is>
       </c>
       <c r="F37" s="53" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G37" s="31" t="inlineStr">
         <is>
-          <t>מעיין רחל דינר, ניתאי שלום, מעיין יוספי, ארבל פרנקו, אוריה תעשה, יונתן לירז, אביה וייל, שירה ספונוב, יערה ריס, חיים שמאי</t>
+          <t>הדר עמדי, נגה שוהם</t>
         </is>
       </c>
       <c r="H37" s="48" t="n"/>
       <c r="I37" s="48" t="inlineStr">
         <is>
-          <t>ניקיונות מוצ"ש</t>
+          <t>סעודה שלישית</t>
         </is>
       </c>
       <c r="J37" s="21" t="n"/>
     </row>
-    <row r="38" ht="90" customHeight="1">
+    <row r="38" ht="30" customHeight="1">
       <c r="A38" s="53" t="inlineStr">
         <is>
           <t>תורנות מוצ"ש</t>
@@ -3412,10 +3412,48 @@
       <c r="C38" s="55" t="n"/>
       <c r="D38" s="48" t="inlineStr">
         <is>
+          <t>ניקיון בית המדרש במוצ"ש</t>
+        </is>
+      </c>
+      <c r="E38" s="21" t="inlineStr">
+        <is>
+          <t>להחזיר את בית המדרש לקדמותו — השולחנות, הכסאות, המחיצה והסידורים, כמו לפני שבת</t>
+        </is>
+      </c>
+      <c r="F38" s="53" t="n">
+        <v>10</v>
+      </c>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>מעיין רחל דינר, ניתאי שלום, מעיין יוספי, ארבל פרנקו, אוריה תעשה, יונתן לירז, אביה וייל, שירה ספונוב, יערה ריס, חיים שמאי</t>
+        </is>
+      </c>
+      <c r="H38" s="48" t="n"/>
+      <c r="I38" s="48" t="inlineStr">
+        <is>
+          <t>ניקיונות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="J38" s="21" t="n"/>
+    </row>
+    <row r="39" ht="90" customHeight="1">
+      <c r="A39" s="53" t="inlineStr">
+        <is>
+          <t>תורנות מוצ"ש</t>
+        </is>
+      </c>
+      <c r="B39" s="56" t="inlineStr">
+        <is>
+          <t>מוצאי שבת</t>
+        </is>
+      </c>
+      <c r="C39" s="55" t="n"/>
+      <c r="D39" s="48" t="inlineStr">
+        <is>
           <t>ניקיון חדר האוכל במוצ"ש</t>
         </is>
       </c>
-      <c r="E38" s="21" t="inlineStr">
+      <c r="E39" s="21" t="inlineStr">
         <is>
           <t>שטיפת הגסטרונומים
 שטיפת הרצפה
@@ -3425,32 +3463,20 @@
 פינוי התנורים</t>
         </is>
       </c>
-      <c r="F38" s="53" t="n">
+      <c r="F39" s="53" t="n">
         <v>12</v>
       </c>
-      <c r="G38" s="31" t="inlineStr">
+      <c r="G39" s="31" t="inlineStr">
         <is>
           <t>איתמר אסנהיים, מאיה פקטר, יובל יצחק, שילת פילפל, איתן וינסטון, רועי צבי סרי, ינון לוי, עמית סיילס, יואב אוחנה, נדב טוקר, אלה מאיר, עמית שי אברהם</t>
         </is>
       </c>
-      <c r="H38" s="48" t="n"/>
-      <c r="I38" s="48" t="inlineStr">
+      <c r="H39" s="48" t="n"/>
+      <c r="I39" s="48" t="inlineStr">
         <is>
           <t>ניקיונות מוצ"ש</t>
         </is>
       </c>
-      <c r="J38" s="21" t="n"/>
-    </row>
-    <row r="39" ht="18" customHeight="1">
-      <c r="A39" s="53" t="n"/>
-      <c r="B39" s="53" t="n"/>
-      <c r="C39" s="55" t="n"/>
-      <c r="D39" s="48" t="n"/>
-      <c r="E39" s="21" t="n"/>
-      <c r="F39" s="53" t="n"/>
-      <c r="G39" s="31" t="n"/>
-      <c r="H39" s="48" t="n"/>
-      <c r="I39" s="48" t="n"/>
       <c r="J39" s="21" t="n"/>
     </row>
     <row r="40" ht="18" customHeight="1">
